--- a/docs/billing-regional-pricing/三组地区最终新价格表.xlsx
+++ b/docs/billing-regional-pricing/三组地区最终新价格表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新价格表" sheetId="1" r:id="Ra0b5267887e541e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pass测算" sheetId="2" r:id="R427179272f604531"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本地显示参考" sheetId="3" r:id="Rfb45c05029b5434b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已采纳44项调整" sheetId="4" r:id="Rfbb49b6bc3414fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新价格表" sheetId="1" r:id="R8032fd7293bb4005"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pass测算" sheetId="2" r:id="R123140bf2554489b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本地显示参考" sheetId="3" r:id="R3b4b8f9b4bcd4188"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已采纳44项调整" sheetId="4" r:id="R7b299209ee2c4d58"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -789,7 +789,7 @@
         <x:v>Z100</x:v>
       </x:c>
       <x:c r="Q2" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R2" s="28" t="n">
         <x:v>79.99</x:v>
@@ -850,7 +850,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q3" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R3" s="29" t="n">
         <x:v>1499</x:v>
@@ -911,7 +911,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q4" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R4" s="28" t="n">
         <x:v>162.99</x:v>
@@ -972,7 +972,7 @@
         <x:v>Z080</x:v>
       </x:c>
       <x:c r="Q5" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R5" s="29" t="n">
         <x:v>499</x:v>
@@ -1033,7 +1033,7 @@
         <x:v>Z065</x:v>
       </x:c>
       <x:c r="Q6" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R6" s="29" t="n">
         <x:v>1699</x:v>
@@ -1094,7 +1094,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q7" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R7" s="29" t="n">
         <x:v>519000</x:v>
@@ -1155,7 +1155,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q8" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R8" s="29" t="n">
         <x:v>48900</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>Z095</x:v>
       </x:c>
       <x:c r="Q9" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R9" s="28" t="n">
         <x:v>108.99</x:v>
@@ -1277,7 +1277,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q10" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R10" s="28" t="n">
         <x:v>113.99</x:v>
@@ -1338,7 +1338,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q11" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R11" s="28" t="n">
         <x:v>88900</x:v>
@@ -1399,7 +1399,7 @@
         <x:v>Z030</x:v>
       </x:c>
       <x:c r="Q12" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R12" s="28" t="n">
         <x:v>1499</x:v>
@@ -1460,7 +1460,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q13" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R13" s="29" t="n">
         <x:v>359000</x:v>
@@ -1521,7 +1521,7 @@
         <x:v>Z085</x:v>
       </x:c>
       <x:c r="Q14" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R14" s="28" t="n">
         <x:v>50.99</x:v>
@@ -1582,7 +1582,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q15" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R15" s="29" t="n">
         <x:v>1599</x:v>
@@ -1643,7 +1643,7 @@
         <x:v>Z090</x:v>
       </x:c>
       <x:c r="Q16" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R16" s="28" t="n">
         <x:v>101.99</x:v>
@@ -1704,7 +1704,7 @@
         <x:v>Z090</x:v>
       </x:c>
       <x:c r="Q17" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R17" s="28" t="n">
         <x:v>91.99</x:v>
@@ -1765,7 +1765,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q18" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R18" s="29" t="n">
         <x:v>4399</x:v>
@@ -1826,7 +1826,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q19" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R19" s="29" t="n">
         <x:v>859</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q20" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R20" s="28" t="n">
         <x:v>460.99</x:v>
@@ -1948,7 +1948,7 @@
         <x:v>Z065</x:v>
       </x:c>
       <x:c r="Q21" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R21" s="29" t="n">
         <x:v>69900</x:v>
@@ -2009,7 +2009,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q22" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R22" s="29" t="n">
         <x:v>20900</x:v>
@@ -2070,7 +2070,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q23" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R23" s="29" t="n">
         <x:v>1999</x:v>
@@ -2131,7 +2131,7 @@
         <x:v>Z045</x:v>
       </x:c>
       <x:c r="Q24" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R24" s="28" t="n">
         <x:v>664.99</x:v>
@@ -2192,7 +2192,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q25" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R25" s="29" t="n">
         <x:v>2599</x:v>
@@ -2253,7 +2253,7 @@
         <x:v>Z080</x:v>
       </x:c>
       <x:c r="Q26" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R26" s="28" t="n">
         <x:v>56.99</x:v>
@@ -2314,7 +2314,7 @@
         <x:v>Z100</x:v>
       </x:c>
       <x:c r="Q27" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R27" s="28" t="n">
         <x:v>70.99</x:v>
@@ -2375,7 +2375,7 @@
         <x:v>Z065</x:v>
       </x:c>
       <x:c r="Q28" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R28" s="29" t="n">
         <x:v>7980</x:v>
@@ -2436,7 +2436,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q29" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R29" s="29" t="n">
         <x:v>2599</x:v>
@@ -2497,7 +2497,7 @@
         <x:v>Z060</x:v>
       </x:c>
       <x:c r="Q30" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R30" s="28" t="n">
         <x:v>42.99</x:v>
@@ -2558,7 +2558,7 @@
         <x:v>Z030</x:v>
       </x:c>
       <x:c r="Q31" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R31" s="29" t="n">
         <x:v>3199</x:v>
@@ -2619,7 +2619,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q32" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R32" s="28" t="n">
         <x:v>27.99</x:v>
@@ -2680,7 +2680,7 @@
         <x:v>Z080</x:v>
       </x:c>
       <x:c r="Q33" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R33" s="29" t="n">
         <x:v>519</x:v>
@@ -2741,7 +2741,7 @@
         <x:v>Z085</x:v>
       </x:c>
       <x:c r="Q34" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R34" s="28" t="n">
         <x:v>119.99</x:v>
@@ -2802,7 +2802,7 @@
         <x:v>Z085</x:v>
       </x:c>
       <x:c r="Q35" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R35" s="28" t="n">
         <x:v>59.99</x:v>
@@ -2863,7 +2863,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q36" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>USD替代已配置</x:v>
       </x:c>
       <x:c r="R36" s="28"/>
       <x:c r="S36" s="28"/>
@@ -2920,7 +2920,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q37" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R37" s="28" t="n">
         <x:v>392.99</x:v>
@@ -2981,7 +2981,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q38" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>USD替代已配置</x:v>
       </x:c>
       <x:c r="R38" s="28"/>
       <x:c r="S38" s="28"/>
@@ -3038,7 +3038,7 @@
         <x:v>Z070</x:v>
       </x:c>
       <x:c r="Q39" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R39" s="28" t="n">
         <x:v>49.99</x:v>
@@ -3099,7 +3099,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q40" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R40" s="29" t="n">
         <x:v>5099</x:v>
@@ -3160,7 +3160,7 @@
         <x:v>Z045</x:v>
       </x:c>
       <x:c r="Q41" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R41" s="28" t="n">
         <x:v>240.99</x:v>
@@ -3221,7 +3221,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q42" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R42" s="29" t="n">
         <x:v>27900</x:v>
@@ -3282,7 +3282,7 @@
         <x:v>Z030</x:v>
       </x:c>
       <x:c r="Q43" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R43" s="28" t="n">
         <x:v>234.99</x:v>
@@ -3343,7 +3343,7 @@
         <x:v>Z030</x:v>
       </x:c>
       <x:c r="Q44" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R44" s="28" t="n">
         <x:v>394.99</x:v>
@@ -3404,7 +3404,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q45" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R45" s="28" t="n">
         <x:v>109.99</x:v>
@@ -3465,7 +3465,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q46" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R46" s="29" t="n">
         <x:v>899</x:v>
@@ -3526,7 +3526,7 @@
         <x:v>Z075</x:v>
       </x:c>
       <x:c r="Q47" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R47" s="28" t="n">
         <x:v>219.99</x:v>
@@ -3587,7 +3587,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q48" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R48" s="28" t="n">
         <x:v>15.99</x:v>
@@ -3648,7 +3648,7 @@
         <x:v>Z055</x:v>
       </x:c>
       <x:c r="Q49" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R49" s="29" t="n">
         <x:v>9199</x:v>
@@ -3709,7 +3709,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q50" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R50" s="28" t="n">
         <x:v>49.99</x:v>
@@ -3770,7 +3770,7 @@
         <x:v>Z045</x:v>
       </x:c>
       <x:c r="Q51" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R51" s="28" t="n">
         <x:v>170.99</x:v>
@@ -3831,7 +3831,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q52" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R52" s="29" t="n">
         <x:v>23900</x:v>
@@ -3892,7 +3892,7 @@
         <x:v>Z060</x:v>
       </x:c>
       <x:c r="Q53" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R53" s="28" t="n">
         <x:v>179.99</x:v>
@@ -3953,7 +3953,7 @@
         <x:v>Z060</x:v>
       </x:c>
       <x:c r="Q54" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R54" s="29" t="n">
         <x:v>1899</x:v>
@@ -4014,7 +4014,7 @@
         <x:v>Z030</x:v>
       </x:c>
       <x:c r="Q55" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R55" s="28" t="n">
         <x:v>40.99</x:v>
@@ -4075,7 +4075,7 @@
         <x:v>Z085</x:v>
       </x:c>
       <x:c r="Q56" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R56" s="28" t="n">
         <x:v>67.99</x:v>
@@ -4136,7 +4136,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q57" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R57" s="28" t="n">
         <x:v>63.99</x:v>
@@ -4197,7 +4197,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q58" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R58" s="28" t="n">
         <x:v>233.99</x:v>
@@ -4258,7 +4258,7 @@
         <x:v>Z075</x:v>
       </x:c>
       <x:c r="Q59" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R59" s="28" t="n">
         <x:v>52.99</x:v>
@@ -4319,7 +4319,7 @@
         <x:v>Z055</x:v>
       </x:c>
       <x:c r="Q60" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R60" s="28" t="n">
         <x:v>38.99</x:v>
@@ -4380,7 +4380,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q61" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R61" s="28" t="n">
         <x:v>213.99</x:v>
@@ -4441,7 +4441,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q62" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>USD替代已配置</x:v>
       </x:c>
       <x:c r="R62" s="28"/>
       <x:c r="S62" s="28"/>
@@ -4498,7 +4498,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q63" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>USD替代已配置</x:v>
       </x:c>
       <x:c r="R63" s="28"/>
       <x:c r="S63" s="28"/>
@@ -4555,7 +4555,7 @@
         <x:v>Z050</x:v>
       </x:c>
       <x:c r="Q64" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R64" s="28" t="n">
         <x:v>39.99</x:v>
@@ -4616,7 +4616,7 @@
         <x:v>Z045</x:v>
       </x:c>
       <x:c r="Q65" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R65" s="28" t="n">
         <x:v>96.99</x:v>
@@ -4677,7 +4677,7 @@
         <x:v>Z065</x:v>
       </x:c>
       <x:c r="Q66" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R66" s="28" t="n">
         <x:v>45.99</x:v>
@@ -4738,7 +4738,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q67" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R67" s="29" t="n">
         <x:v>6599</x:v>
@@ -4799,7 +4799,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q68" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R68" s="29" t="n">
         <x:v>41900</x:v>
@@ -4860,7 +4860,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q69" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R69" s="29" t="n">
         <x:v>63900</x:v>
@@ -4921,7 +4921,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q70" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>USD替代已配置</x:v>
       </x:c>
       <x:c r="R70" s="28"/>
       <x:c r="S70" s="28"/>
@@ -4978,7 +4978,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q71" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R71" s="29" t="n">
         <x:v>319</x:v>
@@ -5039,7 +5039,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q72" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R72" s="29" t="n">
         <x:v>999</x:v>
@@ -5100,7 +5100,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q73" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R73" s="29" t="n">
         <x:v>2599</x:v>
@@ -5161,7 +5161,7 @@
         <x:v>Z055</x:v>
       </x:c>
       <x:c r="Q74" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R74" s="28" t="n">
         <x:v>87.99</x:v>
@@ -5222,7 +5222,7 @@
         <x:v>Z080</x:v>
       </x:c>
       <x:c r="Q75" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R75" s="28" t="n">
         <x:v>56.99</x:v>
@@ -5283,7 +5283,7 @@
         <x:v>Z100</x:v>
       </x:c>
       <x:c r="Q76" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R76" s="28" t="n">
         <x:v>79.99</x:v>
@@ -5344,7 +5344,7 @@
         <x:v>Z055</x:v>
       </x:c>
       <x:c r="Q77" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R77" s="28" t="n">
         <x:v>55.99</x:v>
@@ -5405,7 +5405,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q78" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R78" s="29" t="n">
         <x:v>80900</x:v>
@@ -5466,7 +5466,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q79" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R79" s="29" t="n">
         <x:v>9299</x:v>
@@ -5527,7 +5527,7 @@
         <x:v>Z045</x:v>
       </x:c>
       <x:c r="Q80" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R80" s="29" t="n">
         <x:v>34900</x:v>
@@ -5588,7 +5588,7 @@
         <x:v>Z050</x:v>
       </x:c>
       <x:c r="Q81" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R81" s="29" t="n">
         <x:v>17900</x:v>
@@ -5649,7 +5649,7 @@
         <x:v>Z050</x:v>
       </x:c>
       <x:c r="Q82" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R82" s="28" t="n">
         <x:v>35.99</x:v>
@@ -5710,7 +5710,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q83" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R83" s="28" t="n">
         <x:v>27.99</x:v>
@@ -5771,7 +5771,7 @@
         <x:v>Z080</x:v>
       </x:c>
       <x:c r="Q84" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R84" s="28" t="n">
         <x:v>56.99</x:v>
@@ -5832,7 +5832,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q85" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R85" s="29" t="n">
         <x:v>15900</x:v>
@@ -5893,7 +5893,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q86" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R86" s="28" t="n">
         <x:v>72.99</x:v>
@@ -5954,7 +5954,7 @@
         <x:v>Z030</x:v>
       </x:c>
       <x:c r="Q87" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R87" s="29" t="n">
         <x:v>649</x:v>
@@ -6015,7 +6015,7 @@
         <x:v>Z050</x:v>
       </x:c>
       <x:c r="Q88" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R88" s="29" t="n">
         <x:v>12900</x:v>
@@ -6076,7 +6076,7 @@
         <x:v>Z025</x:v>
       </x:c>
       <x:c r="Q89" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R89" s="29" t="n">
         <x:v>11900</x:v>
@@ -6137,7 +6137,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q90" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R90" s="29" t="n">
         <x:v>14900</x:v>
@@ -6198,7 +6198,7 @@
         <x:v>Z065</x:v>
       </x:c>
       <x:c r="Q91" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>USD替代已配置</x:v>
       </x:c>
       <x:c r="R91" s="28"/>
       <x:c r="S91" s="28"/>
@@ -6255,7 +6255,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q92" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R92" s="29" t="n">
         <x:v>359000</x:v>
@@ -6316,7 +6316,7 @@
         <x:v>Z055</x:v>
       </x:c>
       <x:c r="Q93" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R93" s="28" t="n">
         <x:v>38.99</x:v>
@@ -6377,7 +6377,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q94" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R94" s="29" t="n">
         <x:v>2490000</x:v>
@@ -6438,7 +6438,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q95" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R95" s="29" t="n">
         <x:v>2699</x:v>
@@ -6499,7 +6499,7 @@
         <x:v>Z095</x:v>
       </x:c>
       <x:c r="Q96" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R96" s="28" t="n">
         <x:v>67.99</x:v>
@@ -6560,7 +6560,7 @@
         <x:v>Z045</x:v>
       </x:c>
       <x:c r="Q97" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R97" s="28" t="n">
         <x:v>555.99</x:v>
@@ -6621,7 +6621,7 @@
         <x:v>Z035</x:v>
       </x:c>
       <x:c r="Q98" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R98" s="28" t="n">
         <x:v>501.99</x:v>
@@ -6682,7 +6682,7 @@
         <x:v>Z030</x:v>
       </x:c>
       <x:c r="Q99" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R99" s="29" t="n">
         <x:v>86900</x:v>
@@ -6743,7 +6743,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q100" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R100" s="28" t="n">
         <x:v>27.99</x:v>
@@ -6804,7 +6804,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q101" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R101" s="29" t="n">
         <x:v>33900</x:v>
@@ -6865,7 +6865,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q102" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R102" s="29" t="n">
         <x:v>2399</x:v>
@@ -6926,7 +6926,7 @@
         <x:v>Z100</x:v>
       </x:c>
       <x:c r="Q103" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R103" s="29" t="n">
         <x:v>754.99</x:v>
@@ -6987,7 +6987,7 @@
         <x:v>Z050</x:v>
       </x:c>
       <x:c r="Q104" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>USD替代已配置</x:v>
       </x:c>
       <x:c r="R104" s="28"/>
       <x:c r="S104" s="28"/>
@@ -7044,7 +7044,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q105" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R105" s="28" t="n">
         <x:v>144.99</x:v>
@@ -7105,7 +7105,7 @@
         <x:v>Z050</x:v>
       </x:c>
       <x:c r="Q106" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R106" s="28" t="n">
         <x:v>154.99</x:v>
@@ -7166,7 +7166,7 @@
         <x:v>Z055</x:v>
       </x:c>
       <x:c r="Q107" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R107" s="28" t="n">
         <x:v>43.99</x:v>
@@ -7227,7 +7227,7 @@
         <x:v>Z040</x:v>
       </x:c>
       <x:c r="Q108" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R108" s="29" t="n">
         <x:v>3299</x:v>
@@ -7288,7 +7288,7 @@
         <x:v>Z050</x:v>
       </x:c>
       <x:c r="Q109" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R109" s="28" t="n">
         <x:v>582.99</x:v>
@@ -7349,7 +7349,7 @@
         <x:v>Z055</x:v>
       </x:c>
       <x:c r="Q110" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R110" s="28" t="n">
         <x:v>38.99</x:v>
@@ -7410,7 +7410,7 @@
         <x:v>Z085</x:v>
       </x:c>
       <x:c r="Q111" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R111" s="29" t="n">
         <x:v>673.99</x:v>
@@ -7471,7 +7471,7 @@
         <x:v>Z050</x:v>
       </x:c>
       <x:c r="Q112" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R112" s="28" t="n">
         <x:v>269.99</x:v>
@@ -7532,7 +7532,7 @@
         <x:v>Z020</x:v>
       </x:c>
       <x:c r="Q113" s="13" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R113" s="29" t="n">
         <x:v>189000</x:v>
@@ -7593,7 +7593,7 @@
         <x:v>Z030</x:v>
       </x:c>
       <x:c r="Q114" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R114" s="29" t="n">
         <x:v>799</x:v>
@@ -7654,7 +7654,7 @@
         <x:v>Z080</x:v>
       </x:c>
       <x:c r="Q115" s="18" t="str">
-        <x:v>配置中</x:v>
+        <x:v>已配置</x:v>
       </x:c>
       <x:c r="R115" s="28" t="n">
         <x:v>56.99</x:v>
@@ -7666,7 +7666,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82733869d688412a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f54ca3a75734cd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8355,7 +8355,7 @@
       </x:c>
       <x:c r="K16" s="33"/>
       <x:c r="L16" s="63" t="str">
-        <x:v>沙盒配置正在执行；最终回读通过后更新状态。</x:v>
+        <x:v>当前沙盒Price金额已回读；实际首付、优惠后非零金额和续费尚未测试。</x:v>
       </x:c>
       <x:c r="M16" s="33"/>
       <x:c r="N16" s="33"/>
@@ -40779,7 +40779,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba962653416348dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ea9dce01d804199"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42195,7 +42195,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7285bc2e4214af1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb29e679637840cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/billing-regional-pricing/三组地区最终新价格表.xlsx
+++ b/docs/billing-regional-pricing/三组地区最终新价格表.xlsx
@@ -2,12 +2,1461 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新价格表" sheetId="1" r:id="R8032fd7293bb4005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pass测算" sheetId="2" r:id="R123140bf2554489b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本地显示参考" sheetId="3" r:id="R3b4b8f9b4bcd4188"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已采纳44项调整" sheetId="4" r:id="R7b299209ee2c4d58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新价格表" sheetId="1" r:id="R9964c6bdb2b2459f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pass测算" sheetId="2" r:id="R6747858b1aa147f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本地显示参考" sheetId="3" r:id="Rd0d2ac32534840fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已采纳44项调整" sheetId="4" r:id="R452115a50b484ed4"/>
   </x:sheets>
 </x:workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author/>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="N3" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约18.7699，低额参考约56.8784，按步长1向上取整，固定月价57 INR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：5.99 → 5.9 BRL。参考巴西订阅的,90尾数，将.99小幅收至.90，保持原价格档位。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：40.99 → 40.9 BRL。参考巴西订阅的,90尾数，将.99小幅收至.90，保持原价格档位。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：80.99 → 80.9 BRL。参考巴西订阅的,90尾数，将.99小幅收至.90，保持原价格档位。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：60.99 → 60.9 BRL。参考巴西订阅的,90尾数，将.99小幅收至.90，保持原价格档位。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：194.99 → 194.9 BRL。参考巴西订阅的,90尾数，将.99小幅收至.90，保持原价格档位。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：390.99 → 390.9 BRL。参考巴西订阅的,90尾数，将.99小幅收至.90，保持原价格档位。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别6：731.88 → 730.8 BRL。建议月价联动×12，保留既有Pro年价关系；不另改年付折扣。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：19.99 → 19.9 BRL。参考巴西订阅的,90尾数，将.99小幅收至.90，保持原价格档位。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：9.99 → 9.9 BRL。参考巴西订阅的,90尾数，将.99小幅收至.90，保持原价格档位。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：13.99 → 13.9 BRL。参考巴西订阅的,90尾数，将.99小幅收至.90，保持原价格档位。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约2.0300，低额参考约3.0758，按步长0.1向上取整，固定月价3.1 BRL。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D7" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：18900 → 19000 VND。参考当地整千订阅写法，将百位零碎尾数就近收至整千。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K7" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：64900 → 65000 VND。参考当地整千订阅写法，将百位零碎尾数就近收至整千。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L7" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：31900 → 32000 VND。参考当地整千订阅写法，将百位零碎尾数就近收至整千。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M7" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：44900 → 45000 VND。参考当地整千订阅写法，将百位零碎尾数就近收至整千。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N7" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约6388.6943，低额参考约15487.7439，按步长100向上取整，固定月价15500 VND。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N8" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约589.3447，低额参考约892.9465，按步长10向上取整，固定月价900 ARS。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N10" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约1.4357，低额参考约2.4861，按步长0.1向上取整，固定月价2.5 MYR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N11" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约1084.5923，低额参考约1878.0819，按步长100向上取整，固定月价1900 COP。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N12" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约18.7699，低额参考约37.9190，按步长1向上取整，固定月价38 PHP。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D13" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：13900 → 14000 IDR。参考当地整千订阅写法，将百位零碎尾数就近收至整千。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E13" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：89900 → 90000 IDR。参考当地整千订阅写法，将百位零碎尾数就近收至整千。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K13" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：44900 → 45000 IDR。参考当地整千订阅写法，将百位零碎尾数就近收至整千。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L13" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：22900 → 23000 IDR。参考当地整千订阅写法，将百位零碎尾数就近收至整千。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M13" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：31900 → 32000 IDR。参考当地整千订阅写法，将百位零碎尾数就近收至整千。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N13" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约4452.2761，低额参考约10793.3967，按步长100向上取整，固定月价10800 IDR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N15" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约19.7604，低额参考约29.9400，按步长1向上取整，固定月价30 TRY。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N18" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约54.4277，低额参考约164.9325，按步长10向上取整，固定月价170 PKR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N19" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约10.3507，低额参考约31.3657，按步长1向上取整，固定月价32 EGP。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N20" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约5.6949，低额参考约9.8612，按步长0.1向上取整，固定月价9.9 ZAR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N22" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约262.4317，低额参考约795.2476，按步长10向上取整，固定月价800 NGN。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N23" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约24.2176，低额参考约73.3867，按步长1向上取整，固定月价74 BDT。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N24" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约8.2206，低额参考约11.0715，按步长1向上取整，固定月价12 MXN。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N25" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约32.1416，低额参考约97.3987，按步长1向上取整，固定月价98 ETB。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N29" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约32.1416，低额参考约77.9190，按步长1向上取整，固定月价78 KES。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N30" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.5196，低额参考约0.5249，按步长0.01向上取整，固定月价0.53 EUR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N31" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约40.0655，低额参考约80.9405，按步长1向上取整，固定月价81 DZD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N32" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.3465，低额参考约0.6000，按步长0.01向上取整，固定月价0.6 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="C36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：原候选币种TND不受目标沙盒支持，经用户确认改用USD固定价格。保留Z025倍率区。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N36" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：TND改用USD，采用已批准的Z025固定美元价格。
+类别3：Study Pass倍率原始价约0.2475，低额参考约0.6000，按步长0.01向上取整，固定月价0.60 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N37" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约4.8529，低额参考约8.4033，按步长0.1向上取整，固定月价8.5 BWP。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="C38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：原候选币种GHS不受目标沙盒支持，经用户确认改用USD固定价格。保留Z025倍率区。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N38" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：GHS改用USD，采用已批准的Z025固定美元价格。
+类别3：Study Pass倍率原始价约0.2475，低额参考约0.6000，按步长0.01向上取整，固定月价0.60 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N40" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约64.3327，低额参考约97.4737，按步长1向上取整，固定月价98 JMD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N41" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约2.9710，低额参考约4.0013，按步长0.1向上取整，固定月价4.1 CNY。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N42" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约346.6238，低额参考约1050.3752，按步长100向上取整，固定月价1100 MWK。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N43" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约2.9215，低额参考约5.9020，按步长0.1向上取整，固定月价6 MAD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N44" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约4.9025，低额参考约9.9040，按步长0.1向上取整，固定月价10 NAD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N45" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约1.3367，低额参考约2.0253，按步长0.1向上取整，固定月价2.1 PEN。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N46" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约11.3412，低额参考约27.4937，按步长1向上取整，固定月价28 UAH。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N48" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.1980，低额参考约0.6000，按步长0.01向上取整，固定月价0.6 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N49" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约113.8574，低额参考约125.4627，按步长10向上取整，固定月价130 GYD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N50" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.5938，低额参考约1.7994，按步长0.1向上取整，固定月价1.8 ILS。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N51" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约2.1291，低额参考约2.8674，按步长0.1向上取整，固定月价2.9 RON。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N52" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约292.1466，低额参考约885.2926，按步长10向上取整，固定月价890 RWF。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N53" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约2.2281，低额参考约2.2506，按步长0.1向上取整，固定月价2.3 SAR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N54" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约23.7224，低额参考约23.9620，按步长1向上取整，固定月价24 UYU。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N55" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.4948，低额参考约0.9995，按步长0.01向上取整，固定月价1 AZN。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N57" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.7919，低额参考约1.1998，按步长0.1向上取整，固定月价1.2 BZD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N58" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约2.9215，低额参考约7.0823，按步长0.1向上取整，固定月价7.1 BOB。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N60" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.4763，低额参考约0.5249，按步长0.01向上取整，固定月价0.53 EUR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N61" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约2.6243，低额参考约4.5443，按步长0.1向上取整，固定月价4.6 GTQ。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="C62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：原候选币种IQD不受目标沙盒支持，经用户确认改用USD固定价格。保留Z035倍率区。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N62" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：IQD改用USD，采用已批准的Z035固定美元价格。
+类别3：Study Pass倍率原始价约0.3465，低额参考约0.6000，按步长0.01向上取整，固定月价0.6 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="C63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：原候选币种JOD不受目标沙盒支持，经用户确认改用USD固定价格。保留Z035倍率区。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N63" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：JOD改用USD，采用已批准的Z035固定美元价格。
+类别3：Study Pass倍率原始价约0.3465，低额参考约0.6000，按步长0.01向上取整，固定月价0.6 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N64" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.4950，低额参考约0.6000，按步长0.01向上取整，固定月价0.6 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N65" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约1.1881，低额参考约1.6001，按步长0.1向上取整，固定月价1.7 XCD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N67" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约84.1426，低额参考约203.9820，按步长10向上取整，固定月价210 LKR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N68" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约539.8199，低额参考约1635.8179，按步长100向上取整，固定月价1700 TZS。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N69" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约787.4437，低额参考约2386.1931，按步长100向上取整，固定月价2400 UGX。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="C70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：原候选币种VES不受目标沙盒支持，经用户确认改用USD固定价格。保留Z020倍率区。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N70" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：VES改用USD，采用已批准的Z020固定美元价格。
+类别3：Study Pass倍率原始价约0.1980，低额参考约0.6000，按步长0.01向上取整，固定月价0.6 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N71" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约3.9125，低额参考约11.8559，按步长1向上取整，固定月价12 ZMW。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N72" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约12.8269，低额参考约38.8694，按步长1向上取整，固定月价39 AFN。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N73" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约32.1416，低额参考约48.6993，按步长1向上取整，固定月价49 ALL。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N74" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约1.0890，低额参考约1.2001，按步长0.1向上取整，固定月价1.3 BBD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N77" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.6929，低额参考约0.7635，按步长0.01向上取整，固定月价0.77 BND。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N78" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约985.5428，低额参考约2389.1946，按步长100向上取整，固定月价2400 KHR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N79" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约113.8574，低额参考约345.0225，按步长10向上取整，固定月价350 XAF。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N80" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约435.7684，低额参考约586.8934，按步长10向上取整，固定月价590 CLP。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N81" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约227.7644，低额参考约276.0780，按步长10向上取整，固定月价280 CRC。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N82" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.4330，低额参考约0.5249，按步长0.01向上取整，固定月价0.53 EUR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N83" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.3465，低额参考约0.6000，按步长0.01向上取整，固定月价0.6 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N85" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约199.2505，低额参考约345.0225，按步长10向上取整，固定月价350 XAF。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N86" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.8910，低额参考约1.5428，按步长0.1向上取整，固定月价1.6 GEL。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N87" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约7.8744，低额参考约15.9080，按步长1向上取整，固定月价16 HNL。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N88" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约158.4297，低额参考约192.0360，按步长10向上取整，固定月价200 HUF。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N89" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约143.5723，低额参考约348.0540，按步长10向上取整，固定月价350 XOF。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N90" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约178.2396，低额参考约270.0600，按步长10向上取整，固定月价280 KZT。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="C91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：原候选币种KWD不受目标沙盒支持，经用户确认改用USD固定价格。保留Z065倍率区。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。
+类别5：1.94 → 1.95 USD。编辑建议：倍率零碎尾数就近收至0.05，如1.94→1.95、62.32→62.30。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。
+类别5：62.32 → 62.3 USD。编辑建议：倍率零碎尾数就近收至0.05，如1.94→1.95、62.32→62.30。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。
+类别5：124.72 → 124.7 USD。编辑建议：倍率零碎尾数就近收至0.05，如1.94→1.95、62.32→62.30。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。
+类别5：3.24 → 3.25 USD。编辑建议：倍率零碎尾数就近收至0.05，如1.94→1.95、62.32→62.30。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。
+类别5：4.54 → 4.55 USD。编辑建议：倍率零碎尾数就近收至0.05，如1.94→1.95、62.32→62.30。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N91" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：KWD改用USD，采用已批准的Z065固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N92" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约4402.7514，低额参考约13341.6708，按步长100向上取整，固定月价13400 LAK。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N93" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.4763，低额参考约0.5249，按步长0.01向上取整，固定月价0.53 EUR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N94" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约31151.0755，低额参考约53941.2563，按步长100向上取整，固定月价54000 LBP。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N95" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约33.6273，低额参考约101.9010，按步长10向上取整，固定月价110 LRD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N97" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约6.8834，低额参考约9.2706，按步长0.1向上取整，固定月价9.3 MVR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N98" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约6.1901，低额参考约10.7188，按步长1向上取整，固定月价11 MDL。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N99" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约1084.5923，低额参考约2191.0955，按步长100向上取整，固定月价2200 MNT。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N100" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.3464，低额参考约0.5249，按步长0.01向上取整，固定月价0.53 EUR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N101" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约415.9585，低额参考约1260.4802，按步长100向上取整，固定月价1300 MMK。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N102" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约30.1606，低额参考约91.3957，按步长1向上取整，固定月价92 NPR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：27.99 → 28 NOK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：188.99 → 189 NOK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：376.99 → 377 NOK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：282.99 → 283 NOK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：904.99 → 905 NOK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：1810.99 → 1811 NOK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别6：3395.88 → 3396 NOK。建议月价联动×12，保留既有Pro年价关系；不另改年付折扣。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：93.99 → 94 NOK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：46.99 → 47 NOK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M103" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：65.99 → 66 NOK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="C104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：原候选币种OMR不受目标沙盒支持，经用户确认改用USD固定价格。保留Z050倍率区。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N104" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别4：OMR改用USD，采用已批准的Z050固定美元价格。
+类别3：Study Pass倍率原始价约0.4950，低额参考约0.6000，按步长0.01向上取整，固定月价0.6 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N105" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约1.7824，低额参考约2.7006，按步长0.1向上取整，固定月价2.8 PGK。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N106" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约1.9310，低额参考约2.3406，按步长0.1向上取整，固定月价2.4 PLN。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N107" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.5445，低额参考约0.6000，按步长0.01向上取整，固定月价0.6 USD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N108" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约41.5513，低额参考约62.9565，按步长1向上取整，固定月价63 RSD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N109" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约7.2301，低额参考约8.7638，按步长0.1向上取整，固定月价8.8 SCR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N110" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约0.4763，低额参考约0.5249，按步长0.01向上取整，固定月价0.53 EUR。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="D111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：24.99 → 25 SEK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="E111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：167.99 → 168 SEK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="F111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：336.99 → 337 SEK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="G111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：252.99 → 253 SEK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="H111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：807.99 → 808 SEK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="I111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：1615.99 → 1616 SEK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="J111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别6：3035.88 → 3036 SEK。建议月价联动×12，保留既有Pro年价关系；不另改年付折扣。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="K111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：83.99 → 84 SEK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：41.99 → 42 SEK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="M111" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别5：58.99 → 59 SEK。参考当地整克朗订阅报价，以最近整数克朗简化两位尾数。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N112" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约3.3672，低额参考约4.0814，按步长0.1向上取整，固定月价4.1 TTD。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N113" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约2372.2361，低额参考约7188.5943，按步长100向上取整，固定月价7200 UZS。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="N114" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>类别3：Study Pass倍率原始价约9.9495，低额参考约20.1000，按步长1向上取整，固定月价21 THB。低额参考尚未经过实际扣款验证。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -79,7 +1528,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -104,6 +1553,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF3F5F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFBDE7F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6EFCE"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -163,7 +1627,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="80">
+  <x:cellXfs count="94">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -391,6 +1855,48 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -676,6 +2182,9 @@
     <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="20" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="3" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="26" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="100" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -736,6 +2245,12 @@
       <x:c r="S1" s="27" t="str">
         <x:v>原Pro年（历史）</x:v>
       </x:c>
+      <x:c r="U1" s="62" t="str">
+        <x:v>颜色图例</x:v>
+      </x:c>
+      <x:c r="V1" s="62" t="str">
+        <x:v>改动原因</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="29" customHeight="1">
       <x:c r="A2" s="4" t="str">
@@ -756,7 +2271,7 @@
       <x:c r="F2" s="12" t="n">
         <x:v>39.99</x:v>
       </x:c>
-      <x:c r="G2" s="23" t="n">
+      <x:c r="G2" s="12" t="n">
         <x:v>29.99</x:v>
       </x:c>
       <x:c r="H2" s="12" t="n">
@@ -765,7 +2280,7 @@
       <x:c r="I2" s="12" t="n">
         <x:v>191.88</x:v>
       </x:c>
-      <x:c r="J2" s="23" t="n">
+      <x:c r="J2" s="12" t="n">
         <x:f>ROUND(G2*12,2)</x:f>
         <x:v>359.88</x:v>
       </x:c>
@@ -797,6 +2312,12 @@
       <x:c r="S2" s="28" t="n">
         <x:v>383.88</x:v>
       </x:c>
+      <x:c r="U2" s="91" t="str">
+        <x:v>浅黄色（类别3）</x:v>
+      </x:c>
+      <x:c r="V2" s="90" t="str">
+        <x:v>Study Pass低额上调，并按既定步长向上取整。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="29" customHeight="1">
       <x:c r="A3" s="4" t="str">
@@ -817,7 +2338,7 @@
       <x:c r="F3" s="15" t="n">
         <x:v>759</x:v>
       </x:c>
-      <x:c r="G3" s="24" t="n">
+      <x:c r="G3" s="15" t="n">
         <x:v>569</x:v>
       </x:c>
       <x:c r="H3" s="15" t="n">
@@ -826,7 +2347,7 @@
       <x:c r="I3" s="15" t="n">
         <x:v>3699</x:v>
       </x:c>
-      <x:c r="J3" s="24" t="n">
+      <x:c r="J3" s="15" t="n">
         <x:f>ROUND(G3*12,2)</x:f>
         <x:v>6828</x:v>
       </x:c>
@@ -839,7 +2360,7 @@
       <x:c r="M3" s="15" t="n">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="N3" s="15" t="n">
+      <x:c r="N3" s="80" t="n">
         <x:f>'Pass测算'!J2</x:f>
         <x:v>57</x:v>
       </x:c>
@@ -857,6 +2378,12 @@
       </x:c>
       <x:c r="S3" s="29" t="n">
         <x:v>7299</x:v>
+      </x:c>
+      <x:c r="U3" s="92" t="str">
+        <x:v>浅绿色（类别4）</x:v>
+      </x:c>
+      <x:c r="V3" s="90" t="str">
+        <x:v>原候选币种不受目标沙盒支持，改用已批准USD固定价。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="29" customHeight="1">
@@ -869,38 +2396,38 @@
       <x:c r="C4" s="13" t="str">
         <x:v>BRL</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="n">
+      <x:c r="D4" s="81" t="n">
         <x:v>5.9</x:v>
       </x:c>
-      <x:c r="E4" s="12" t="n">
+      <x:c r="E4" s="81" t="n">
         <x:v>40.9</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="n">
+      <x:c r="F4" s="81" t="n">
         <x:v>80.9</x:v>
       </x:c>
-      <x:c r="G4" s="23" t="n">
+      <x:c r="G4" s="81" t="n">
         <x:v>60.9</x:v>
       </x:c>
-      <x:c r="H4" s="12" t="n">
+      <x:c r="H4" s="81" t="n">
         <x:v>194.9</x:v>
       </x:c>
-      <x:c r="I4" s="12" t="n">
+      <x:c r="I4" s="81" t="n">
         <x:v>390.9</x:v>
       </x:c>
-      <x:c r="J4" s="23" t="n">
+      <x:c r="J4" s="81" t="n">
         <x:f>ROUND(G4*12,2)</x:f>
         <x:v>730.8</x:v>
       </x:c>
-      <x:c r="K4" s="12" t="n">
+      <x:c r="K4" s="81" t="n">
         <x:v>19.9</x:v>
       </x:c>
-      <x:c r="L4" s="12" t="n">
+      <x:c r="L4" s="81" t="n">
         <x:v>9.9</x:v>
       </x:c>
-      <x:c r="M4" s="12" t="n">
+      <x:c r="M4" s="81" t="n">
         <x:v>13.9</x:v>
       </x:c>
-      <x:c r="N4" s="14" t="n">
+      <x:c r="N4" s="82" t="n">
         <x:f>'Pass测算'!J49</x:f>
         <x:v>3.1</x:v>
       </x:c>
@@ -918,6 +2445,12 @@
       </x:c>
       <x:c r="S4" s="28" t="n">
         <x:v>780.99</x:v>
+      </x:c>
+      <x:c r="U4" s="93" t="str">
+        <x:v>浅蓝色（类别5、6）</x:v>
+      </x:c>
+      <x:c r="V4" s="90" t="str">
+        <x:v>本地标价尾数微调，以及Pro年价随月价×12联动。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="29" customHeight="1">
@@ -939,7 +2472,7 @@
       <x:c r="F5" s="19" t="n">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G5" s="25" t="n">
+      <x:c r="G5" s="19" t="n">
         <x:v>189</x:v>
       </x:c>
       <x:c r="H5" s="19" t="n">
@@ -948,7 +2481,7 @@
       <x:c r="I5" s="19" t="n">
         <x:v>1199</x:v>
       </x:c>
-      <x:c r="J5" s="25" t="n">
+      <x:c r="J5" s="19" t="n">
         <x:f>ROUND(G5*12,2)</x:f>
         <x:v>2268</x:v>
       </x:c>
@@ -980,6 +2513,12 @@
       <x:c r="S5" s="29" t="n">
         <x:v>2399</x:v>
       </x:c>
+      <x:c r="U5" s="90" t="str">
+        <x:v>重叠标记</x:v>
+      </x:c>
+      <x:c r="V5" s="90" t="str">
+        <x:v>同一金额按浅蓝＞浅黄＞浅绿显示，单元格批注保留全部原因。</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="29" customHeight="1">
       <x:c r="A6" s="16" t="str">
@@ -1000,7 +2539,7 @@
       <x:c r="F6" s="19" t="n">
         <x:v>839</x:v>
       </x:c>
-      <x:c r="G6" s="25" t="n">
+      <x:c r="G6" s="19" t="n">
         <x:v>629</x:v>
       </x:c>
       <x:c r="H6" s="19" t="n">
@@ -1009,7 +2548,7 @@
       <x:c r="I6" s="19" t="n">
         <x:v>3999</x:v>
       </x:c>
-      <x:c r="J6" s="25" t="n">
+      <x:c r="J6" s="19" t="n">
         <x:f>ROUND(G6*12,2)</x:f>
         <x:v>7548</x:v>
       </x:c>
@@ -1041,6 +2580,12 @@
       <x:c r="S6" s="29" t="n">
         <x:v>8099</x:v>
       </x:c>
+      <x:c r="U6" s="90" t="str">
+        <x:v>USD重叠示例</x:v>
+      </x:c>
+      <x:c r="V6" s="90" t="str">
+        <x:v>科威特尾数金额浅蓝、币种格浅绿；USD替代且低额上调的Pass浅黄。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="29" customHeight="1">
       <x:c r="A7" s="4" t="str">
@@ -1052,7 +2597,7 @@
       <x:c r="C7" s="13" t="str">
         <x:v>VND</x:v>
       </x:c>
-      <x:c r="D7" s="15" t="n">
+      <x:c r="D7" s="83" t="n">
         <x:v>19000</x:v>
       </x:c>
       <x:c r="E7" s="15" t="n">
@@ -1061,7 +2606,7 @@
       <x:c r="F7" s="15" t="n">
         <x:v>259000</x:v>
       </x:c>
-      <x:c r="G7" s="24" t="n">
+      <x:c r="G7" s="15" t="n">
         <x:v>189000</x:v>
       </x:c>
       <x:c r="H7" s="15" t="n">
@@ -1070,20 +2615,20 @@
       <x:c r="I7" s="15" t="n">
         <x:v>1239000</x:v>
       </x:c>
-      <x:c r="J7" s="24" t="n">
+      <x:c r="J7" s="15" t="n">
         <x:f>ROUND(G7*12,2)</x:f>
         <x:v>2268000</x:v>
       </x:c>
-      <x:c r="K7" s="15" t="n">
+      <x:c r="K7" s="83" t="n">
         <x:v>65000</x:v>
       </x:c>
-      <x:c r="L7" s="15" t="n">
+      <x:c r="L7" s="83" t="n">
         <x:v>32000</x:v>
       </x:c>
-      <x:c r="M7" s="15" t="n">
+      <x:c r="M7" s="83" t="n">
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="N7" s="15" t="n">
+      <x:c r="N7" s="80" t="n">
         <x:f>'Pass测算'!J22</x:f>
         <x:v>15500</x:v>
       </x:c>
@@ -1101,6 +2646,12 @@
       </x:c>
       <x:c r="S7" s="29" t="n">
         <x:v>2490000</x:v>
+      </x:c>
+      <x:c r="U7" s="90" t="str">
+        <x:v>未着色金额</x:v>
+      </x:c>
+      <x:c r="V7" s="90" t="str">
+        <x:v>未涉及以上四类调整。单纯补价、采用新Pro列和显示写法不在此次标色范围。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -1122,7 +2673,7 @@
       <x:c r="F8" s="15" t="n">
         <x:v>23900</x:v>
       </x:c>
-      <x:c r="G8" s="24" t="n">
+      <x:c r="G8" s="15" t="n">
         <x:v>17900</x:v>
       </x:c>
       <x:c r="H8" s="15" t="n">
@@ -1131,7 +2682,7 @@
       <x:c r="I8" s="15" t="n">
         <x:v>115900</x:v>
       </x:c>
-      <x:c r="J8" s="24" t="n">
+      <x:c r="J8" s="15" t="n">
         <x:f>ROUND(G8*12,2)</x:f>
         <x:v>214800</x:v>
       </x:c>
@@ -1144,7 +2695,7 @@
       <x:c r="M8" s="15" t="n">
         <x:v>4199</x:v>
       </x:c>
-      <x:c r="N8" s="15" t="n">
+      <x:c r="N8" s="80" t="n">
         <x:f>'Pass测算'!J50</x:f>
         <x:v>900</x:v>
       </x:c>
@@ -1183,7 +2734,7 @@
       <x:c r="F9" s="12" t="n">
         <x:v>54.99</x:v>
       </x:c>
-      <x:c r="G9" s="23" t="n">
+      <x:c r="G9" s="12" t="n">
         <x:v>40.99</x:v>
       </x:c>
       <x:c r="H9" s="12" t="n">
@@ -1192,7 +2743,7 @@
       <x:c r="I9" s="12" t="n">
         <x:v>261.99</x:v>
       </x:c>
-      <x:c r="J9" s="23" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:f>ROUND(G9*12,2)</x:f>
         <x:v>491.88</x:v>
       </x:c>
@@ -1244,7 +2795,7 @@
       <x:c r="F10" s="12" t="n">
         <x:v>56.99</x:v>
       </x:c>
-      <x:c r="G10" s="23" t="n">
+      <x:c r="G10" s="12" t="n">
         <x:v>42.99</x:v>
       </x:c>
       <x:c r="H10" s="12" t="n">
@@ -1253,7 +2804,7 @@
       <x:c r="I10" s="12" t="n">
         <x:v>273.99</x:v>
       </x:c>
-      <x:c r="J10" s="23" t="n">
+      <x:c r="J10" s="12" t="n">
         <x:f>ROUND(G10*12,2)</x:f>
         <x:v>515.88</x:v>
       </x:c>
@@ -1266,7 +2817,7 @@
       <x:c r="M10" s="12" t="n">
         <x:v>9.99</x:v>
       </x:c>
-      <x:c r="N10" s="14" t="n">
+      <x:c r="N10" s="82" t="n">
         <x:f>'Pass测算'!J39</x:f>
         <x:v>2.5</x:v>
       </x:c>
@@ -1305,7 +2856,7 @@
       <x:c r="F11" s="12" t="n">
         <x:v>44900</x:v>
       </x:c>
-      <x:c r="G11" s="23" t="n">
+      <x:c r="G11" s="12" t="n">
         <x:v>33900</x:v>
       </x:c>
       <x:c r="H11" s="12" t="n">
@@ -1314,7 +2865,7 @@
       <x:c r="I11" s="12" t="n">
         <x:v>219000</x:v>
       </x:c>
-      <x:c r="J11" s="23" t="n">
+      <x:c r="J11" s="12" t="n">
         <x:f>ROUND(G11*12,2)</x:f>
         <x:v>406800</x:v>
       </x:c>
@@ -1327,7 +2878,7 @@
       <x:c r="M11" s="12" t="n">
         <x:v>7799</x:v>
       </x:c>
-      <x:c r="N11" s="15" t="n">
+      <x:c r="N11" s="80" t="n">
         <x:f>'Pass测算'!J40</x:f>
         <x:v>1900</x:v>
       </x:c>
@@ -1366,7 +2917,7 @@
       <x:c r="F12" s="12" t="n">
         <x:v>759</x:v>
       </x:c>
-      <x:c r="G12" s="23" t="n">
+      <x:c r="G12" s="12" t="n">
         <x:v>569</x:v>
       </x:c>
       <x:c r="H12" s="12" t="n">
@@ -1375,7 +2926,7 @@
       <x:c r="I12" s="12" t="n">
         <x:v>3599</x:v>
       </x:c>
-      <x:c r="J12" s="23" t="n">
+      <x:c r="J12" s="12" t="n">
         <x:f>ROUND(G12*12,2)</x:f>
         <x:v>6828</x:v>
       </x:c>
@@ -1388,7 +2939,7 @@
       <x:c r="M12" s="12" t="n">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="N12" s="15" t="n">
+      <x:c r="N12" s="80" t="n">
         <x:f>'Pass测算'!J31</x:f>
         <x:v>38</x:v>
       </x:c>
@@ -1418,16 +2969,16 @@
       <x:c r="C13" s="18" t="str">
         <x:v>IDR</x:v>
       </x:c>
-      <x:c r="D13" s="19" t="n">
+      <x:c r="D13" s="84" t="n">
         <x:v>14000</x:v>
       </x:c>
-      <x:c r="E13" s="19" t="n">
+      <x:c r="E13" s="84" t="n">
         <x:v>90000</x:v>
       </x:c>
       <x:c r="F13" s="19" t="n">
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="G13" s="25" t="n">
+      <x:c r="G13" s="19" t="n">
         <x:v>139000</x:v>
       </x:c>
       <x:c r="H13" s="19" t="n">
@@ -1436,20 +2987,20 @@
       <x:c r="I13" s="19" t="n">
         <x:v>869000</x:v>
       </x:c>
-      <x:c r="J13" s="25" t="n">
+      <x:c r="J13" s="19" t="n">
         <x:f>ROUND(G13*12,2)</x:f>
         <x:v>1668000</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="84" t="n">
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="L13" s="19" t="n">
+      <x:c r="L13" s="84" t="n">
         <x:v>23000</x:v>
       </x:c>
-      <x:c r="M13" s="19" t="n">
+      <x:c r="M13" s="84" t="n">
         <x:v>32000</x:v>
       </x:c>
-      <x:c r="N13" s="19" t="n">
+      <x:c r="N13" s="85" t="n">
         <x:f>'Pass测算'!J23</x:f>
         <x:v>10800</x:v>
       </x:c>
@@ -1488,7 +3039,7 @@
       <x:c r="F14" s="12" t="n">
         <x:v>25.99</x:v>
       </x:c>
-      <x:c r="G14" s="23" t="n">
+      <x:c r="G14" s="12" t="n">
         <x:v>18.99</x:v>
       </x:c>
       <x:c r="H14" s="12" t="n">
@@ -1497,7 +3048,7 @@
       <x:c r="I14" s="12" t="n">
         <x:v>121.99</x:v>
       </x:c>
-      <x:c r="J14" s="23" t="n">
+      <x:c r="J14" s="12" t="n">
         <x:f>ROUND(G14*12,2)</x:f>
         <x:v>227.88</x:v>
       </x:c>
@@ -1549,7 +3100,7 @@
       <x:c r="F15" s="19" t="n">
         <x:v>789</x:v>
       </x:c>
-      <x:c r="G15" s="25" t="n">
+      <x:c r="G15" s="19" t="n">
         <x:v>599</x:v>
       </x:c>
       <x:c r="H15" s="19" t="n">
@@ -1558,7 +3109,7 @@
       <x:c r="I15" s="19" t="n">
         <x:v>3799</x:v>
       </x:c>
-      <x:c r="J15" s="25" t="n">
+      <x:c r="J15" s="19" t="n">
         <x:f>ROUND(G15*12,2)</x:f>
         <x:v>7188</x:v>
       </x:c>
@@ -1571,7 +3122,7 @@
       <x:c r="M15" s="19" t="n">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="N15" s="19" t="n">
+      <x:c r="N15" s="85" t="n">
         <x:f>'Pass测算'!J51</x:f>
         <x:v>30</x:v>
       </x:c>
@@ -1610,7 +3161,7 @@
       <x:c r="F16" s="12" t="n">
         <x:v>50.99</x:v>
       </x:c>
-      <x:c r="G16" s="23" t="n">
+      <x:c r="G16" s="12" t="n">
         <x:v>37.99</x:v>
       </x:c>
       <x:c r="H16" s="12" t="n">
@@ -1619,7 +3170,7 @@
       <x:c r="I16" s="12" t="n">
         <x:v>243.99</x:v>
       </x:c>
-      <x:c r="J16" s="23" t="n">
+      <x:c r="J16" s="12" t="n">
         <x:f>ROUND(G16*12,2)</x:f>
         <x:v>455.88</x:v>
       </x:c>
@@ -1671,7 +3222,7 @@
       <x:c r="F17" s="12" t="n">
         <x:v>45.99</x:v>
       </x:c>
-      <x:c r="G17" s="23" t="n">
+      <x:c r="G17" s="12" t="n">
         <x:v>34.99</x:v>
       </x:c>
       <x:c r="H17" s="12" t="n">
@@ -1680,7 +3231,7 @@
       <x:c r="I17" s="12" t="n">
         <x:v>220.99</x:v>
       </x:c>
-      <x:c r="J17" s="23" t="n">
+      <x:c r="J17" s="12" t="n">
         <x:f>ROUND(G17*12,2)</x:f>
         <x:v>419.88</x:v>
       </x:c>
@@ -1732,7 +3283,7 @@
       <x:c r="F18" s="15" t="n">
         <x:v>2199</x:v>
       </x:c>
-      <x:c r="G18" s="24" t="n">
+      <x:c r="G18" s="15" t="n">
         <x:v>1699</x:v>
       </x:c>
       <x:c r="H18" s="15" t="n">
@@ -1741,7 +3292,7 @@
       <x:c r="I18" s="15" t="n">
         <x:v>10599</x:v>
       </x:c>
-      <x:c r="J18" s="24" t="n">
+      <x:c r="J18" s="15" t="n">
         <x:f>ROUND(G18*12,2)</x:f>
         <x:v>20388</x:v>
       </x:c>
@@ -1754,7 +3305,7 @@
       <x:c r="M18" s="15" t="n">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="N18" s="15" t="n">
+      <x:c r="N18" s="80" t="n">
         <x:f>'Pass测算'!J3</x:f>
         <x:v>170</x:v>
       </x:c>
@@ -1793,7 +3344,7 @@
       <x:c r="F19" s="15" t="n">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="G19" s="24" t="n">
+      <x:c r="G19" s="15" t="n">
         <x:v>319</x:v>
       </x:c>
       <x:c r="H19" s="15" t="n">
@@ -1802,7 +3353,7 @@
       <x:c r="I19" s="15" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J19" s="24" t="n">
+      <x:c r="J19" s="15" t="n">
         <x:f>ROUND(G19*12,2)</x:f>
         <x:v>3828</x:v>
       </x:c>
@@ -1815,7 +3366,7 @@
       <x:c r="M19" s="15" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="N19" s="15" t="n">
+      <x:c r="N19" s="80" t="n">
         <x:f>'Pass测算'!J4</x:f>
         <x:v>32</x:v>
       </x:c>
@@ -1854,7 +3405,7 @@
       <x:c r="F20" s="12" t="n">
         <x:v>230.99</x:v>
       </x:c>
-      <x:c r="G20" s="23" t="n">
+      <x:c r="G20" s="12" t="n">
         <x:v>172.99</x:v>
       </x:c>
       <x:c r="H20" s="12" t="n">
@@ -1863,7 +3414,7 @@
       <x:c r="I20" s="12" t="n">
         <x:v>1105.99</x:v>
       </x:c>
-      <x:c r="J20" s="23" t="n">
+      <x:c r="J20" s="12" t="n">
         <x:f>ROUND(G20*12,2)</x:f>
         <x:v>2075.88</x:v>
       </x:c>
@@ -1876,7 +3427,7 @@
       <x:c r="M20" s="12" t="n">
         <x:v>39.99</x:v>
       </x:c>
-      <x:c r="N20" s="14" t="n">
+      <x:c r="N20" s="82" t="n">
         <x:f>'Pass测算'!J41</x:f>
         <x:v>9.9</x:v>
       </x:c>
@@ -1915,7 +3466,7 @@
       <x:c r="F21" s="19" t="n">
         <x:v>34900</x:v>
       </x:c>
-      <x:c r="G21" s="25" t="n">
+      <x:c r="G21" s="19" t="n">
         <x:v>25900</x:v>
       </x:c>
       <x:c r="H21" s="19" t="n">
@@ -1924,7 +3475,7 @@
       <x:c r="I21" s="19" t="n">
         <x:v>166900</x:v>
       </x:c>
-      <x:c r="J21" s="25" t="n">
+      <x:c r="J21" s="19" t="n">
         <x:f>ROUND(G21*12,2)</x:f>
         <x:v>310800</x:v>
       </x:c>
@@ -1976,7 +3527,7 @@
       <x:c r="F22" s="15" t="n">
         <x:v>10900</x:v>
       </x:c>
-      <x:c r="G22" s="24" t="n">
+      <x:c r="G22" s="15" t="n">
         <x:v>7999</x:v>
       </x:c>
       <x:c r="H22" s="15" t="n">
@@ -1985,7 +3536,7 @@
       <x:c r="I22" s="15" t="n">
         <x:v>51900</x:v>
       </x:c>
-      <x:c r="J22" s="24" t="n">
+      <x:c r="J22" s="15" t="n">
         <x:f>ROUND(G22*12,2)</x:f>
         <x:v>95988</x:v>
       </x:c>
@@ -1998,7 +3549,7 @@
       <x:c r="M22" s="15" t="n">
         <x:v>1899</x:v>
       </x:c>
-      <x:c r="N22" s="15" t="n">
+      <x:c r="N22" s="80" t="n">
         <x:f>'Pass测算'!J5</x:f>
         <x:v>800</x:v>
       </x:c>
@@ -2037,7 +3588,7 @@
       <x:c r="F23" s="15" t="n">
         <x:v>989</x:v>
       </x:c>
-      <x:c r="G23" s="24" t="n">
+      <x:c r="G23" s="15" t="n">
         <x:v>739</x:v>
       </x:c>
       <x:c r="H23" s="15" t="n">
@@ -2046,7 +3597,7 @@
       <x:c r="I23" s="15" t="n">
         <x:v>4699</x:v>
       </x:c>
-      <x:c r="J23" s="24" t="n">
+      <x:c r="J23" s="15" t="n">
         <x:f>ROUND(G23*12,2)</x:f>
         <x:v>8868</x:v>
       </x:c>
@@ -2059,7 +3610,7 @@
       <x:c r="M23" s="15" t="n">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="N23" s="15" t="n">
+      <x:c r="N23" s="80" t="n">
         <x:f>'Pass测算'!J6</x:f>
         <x:v>74</x:v>
       </x:c>
@@ -2098,7 +3649,7 @@
       <x:c r="F24" s="12" t="n">
         <x:v>331.99</x:v>
       </x:c>
-      <x:c r="G24" s="23" t="n">
+      <x:c r="G24" s="12" t="n">
         <x:v>248.99</x:v>
       </x:c>
       <x:c r="H24" s="12" t="n">
@@ -2107,7 +3658,7 @@
       <x:c r="I24" s="12" t="n">
         <x:v>1594.99</x:v>
       </x:c>
-      <x:c r="J24" s="23" t="n">
+      <x:c r="J24" s="12" t="n">
         <x:f>ROUND(G24*12,2)</x:f>
         <x:v>2987.88</x:v>
       </x:c>
@@ -2120,7 +3671,7 @@
       <x:c r="M24" s="12" t="n">
         <x:v>57.99</x:v>
       </x:c>
-      <x:c r="N24" s="15" t="n">
+      <x:c r="N24" s="80" t="n">
         <x:f>'Pass测算'!J60</x:f>
         <x:v>12</x:v>
       </x:c>
@@ -2159,7 +3710,7 @@
       <x:c r="F25" s="15" t="n">
         <x:v>1299</x:v>
       </x:c>
-      <x:c r="G25" s="24" t="n">
+      <x:c r="G25" s="15" t="n">
         <x:v>969</x:v>
       </x:c>
       <x:c r="H25" s="15" t="n">
@@ -2168,7 +3719,7 @@
       <x:c r="I25" s="15" t="n">
         <x:v>6199</x:v>
       </x:c>
-      <x:c r="J25" s="24" t="n">
+      <x:c r="J25" s="15" t="n">
         <x:f>ROUND(G25*12,2)</x:f>
         <x:v>11628</x:v>
       </x:c>
@@ -2181,7 +3732,7 @@
       <x:c r="M25" s="15" t="n">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="N25" s="15" t="n">
+      <x:c r="N25" s="80" t="n">
         <x:f>'Pass测算'!J7</x:f>
         <x:v>98</x:v>
       </x:c>
@@ -2220,7 +3771,7 @@
       <x:c r="F26" s="21" t="n">
         <x:v>27.99</x:v>
       </x:c>
-      <x:c r="G26" s="26" t="n">
+      <x:c r="G26" s="21" t="n">
         <x:v>20.99</x:v>
       </x:c>
       <x:c r="H26" s="21" t="n">
@@ -2229,7 +3780,7 @@
       <x:c r="I26" s="21" t="n">
         <x:v>136.99</x:v>
       </x:c>
-      <x:c r="J26" s="26" t="n">
+      <x:c r="J26" s="21" t="n">
         <x:f>ROUND(G26*12,2)</x:f>
         <x:v>251.88</x:v>
       </x:c>
@@ -2281,7 +3832,7 @@
       <x:c r="F27" s="12" t="n">
         <x:v>35.99</x:v>
       </x:c>
-      <x:c r="G27" s="23" t="n">
+      <x:c r="G27" s="12" t="n">
         <x:v>26.99</x:v>
       </x:c>
       <x:c r="H27" s="12" t="n">
@@ -2290,7 +3841,7 @@
       <x:c r="I27" s="12" t="n">
         <x:v>170.99</x:v>
       </x:c>
-      <x:c r="J27" s="23" t="n">
+      <x:c r="J27" s="12" t="n">
         <x:f>ROUND(G27*12,2)</x:f>
         <x:v>323.88</x:v>
       </x:c>
@@ -2342,7 +3893,7 @@
       <x:c r="F28" s="15" t="n">
         <x:v>3980</x:v>
       </x:c>
-      <x:c r="G28" s="24" t="n">
+      <x:c r="G28" s="15" t="n">
         <x:v>2980</x:v>
       </x:c>
       <x:c r="H28" s="15" t="n">
@@ -2351,7 +3902,7 @@
       <x:c r="I28" s="15" t="n">
         <x:v>18980</x:v>
       </x:c>
-      <x:c r="J28" s="24" t="n">
+      <x:c r="J28" s="15" t="n">
         <x:f>ROUND(G28*12,2)</x:f>
         <x:v>35760</x:v>
       </x:c>
@@ -2403,7 +3954,7 @@
       <x:c r="F29" s="15" t="n">
         <x:v>1299</x:v>
       </x:c>
-      <x:c r="G29" s="24" t="n">
+      <x:c r="G29" s="15" t="n">
         <x:v>969</x:v>
       </x:c>
       <x:c r="H29" s="15" t="n">
@@ -2412,7 +3963,7 @@
       <x:c r="I29" s="15" t="n">
         <x:v>6199</x:v>
       </x:c>
-      <x:c r="J29" s="24" t="n">
+      <x:c r="J29" s="15" t="n">
         <x:f>ROUND(G29*12,2)</x:f>
         <x:v>11628</x:v>
       </x:c>
@@ -2425,7 +3976,7 @@
       <x:c r="M29" s="15" t="n">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="N29" s="15" t="n">
+      <x:c r="N29" s="80" t="n">
         <x:f>'Pass测算'!J24</x:f>
         <x:v>78</x:v>
       </x:c>
@@ -2464,7 +4015,7 @@
       <x:c r="F30" s="12" t="n">
         <x:v>20.99</x:v>
       </x:c>
-      <x:c r="G30" s="23" t="n">
+      <x:c r="G30" s="12" t="n">
         <x:v>15.99</x:v>
       </x:c>
       <x:c r="H30" s="12" t="n">
@@ -2473,7 +4024,7 @@
       <x:c r="I30" s="12" t="n">
         <x:v>101.99</x:v>
       </x:c>
-      <x:c r="J30" s="23" t="n">
+      <x:c r="J30" s="12" t="n">
         <x:f>ROUND(G30*12,2)</x:f>
         <x:v>191.88</x:v>
       </x:c>
@@ -2486,7 +4037,7 @@
       <x:c r="M30" s="12" t="n">
         <x:v>3.49</x:v>
       </x:c>
-      <x:c r="N30" s="14" t="n">
+      <x:c r="N30" s="82" t="n">
         <x:f>'Pass测算'!J78</x:f>
         <x:v>0.53</x:v>
       </x:c>
@@ -2525,7 +4076,7 @@
       <x:c r="F31" s="15" t="n">
         <x:v>1599</x:v>
       </x:c>
-      <x:c r="G31" s="24" t="n">
+      <x:c r="G31" s="15" t="n">
         <x:v>1199</x:v>
       </x:c>
       <x:c r="H31" s="15" t="n">
@@ -2534,7 +4085,7 @@
       <x:c r="I31" s="15" t="n">
         <x:v>7699</x:v>
       </x:c>
-      <x:c r="J31" s="24" t="n">
+      <x:c r="J31" s="15" t="n">
         <x:f>ROUND(G31*12,2)</x:f>
         <x:v>14388</x:v>
       </x:c>
@@ -2547,7 +4098,7 @@
       <x:c r="M31" s="15" t="n">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="N31" s="15" t="n">
+      <x:c r="N31" s="80" t="n">
         <x:f>'Pass测算'!J32</x:f>
         <x:v>81</x:v>
       </x:c>
@@ -2586,7 +4137,7 @@
       <x:c r="F32" s="12" t="n">
         <x:v>13.99</x:v>
       </x:c>
-      <x:c r="G32" s="23" t="n">
+      <x:c r="G32" s="12" t="n">
         <x:v>10.99</x:v>
       </x:c>
       <x:c r="H32" s="12" t="n">
@@ -2595,7 +4146,7 @@
       <x:c r="I32" s="12" t="n">
         <x:v>66.99</x:v>
       </x:c>
-      <x:c r="J32" s="23" t="n">
+      <x:c r="J32" s="12" t="n">
         <x:f>ROUND(G32*12,2)</x:f>
         <x:v>131.88</x:v>
       </x:c>
@@ -2608,7 +4159,7 @@
       <x:c r="M32" s="12" t="n">
         <x:v>2.49</x:v>
       </x:c>
-      <x:c r="N32" s="14" t="n">
+      <x:c r="N32" s="82" t="n">
         <x:f>'Pass测算'!J42</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -2647,7 +4198,7 @@
       <x:c r="F33" s="15" t="n">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="G33" s="24" t="n">
+      <x:c r="G33" s="15" t="n">
         <x:v>199</x:v>
       </x:c>
       <x:c r="H33" s="15" t="n">
@@ -2656,7 +4207,7 @@
       <x:c r="I33" s="15" t="n">
         <x:v>1249</x:v>
       </x:c>
-      <x:c r="J33" s="24" t="n">
+      <x:c r="J33" s="15" t="n">
         <x:f>ROUND(G33*12,2)</x:f>
         <x:v>2388</x:v>
       </x:c>
@@ -2708,7 +4259,7 @@
       <x:c r="F34" s="12" t="n">
         <x:v>59.99</x:v>
       </x:c>
-      <x:c r="G34" s="23" t="n">
+      <x:c r="G34" s="12" t="n">
         <x:v>44.99</x:v>
       </x:c>
       <x:c r="H34" s="12" t="n">
@@ -2717,7 +4268,7 @@
       <x:c r="I34" s="12" t="n">
         <x:v>287.99</x:v>
       </x:c>
-      <x:c r="J34" s="23" t="n">
+      <x:c r="J34" s="12" t="n">
         <x:f>ROUND(G34*12,2)</x:f>
         <x:v>539.88</x:v>
       </x:c>
@@ -2769,7 +4320,7 @@
       <x:c r="F35" s="12" t="n">
         <x:v>29.99</x:v>
       </x:c>
-      <x:c r="G35" s="23" t="n">
+      <x:c r="G35" s="12" t="n">
         <x:v>22.99</x:v>
       </x:c>
       <x:c r="H35" s="12" t="n">
@@ -2778,7 +4329,7 @@
       <x:c r="I35" s="12" t="n">
         <x:v>144.99</x:v>
       </x:c>
-      <x:c r="J35" s="23" t="n">
+      <x:c r="J35" s="12" t="n">
         <x:f>ROUND(G35*12,2)</x:f>
         <x:v>275.88</x:v>
       </x:c>
@@ -2818,41 +4369,41 @@
       <x:c r="B36" s="10" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="C36" s="13" t="str">
+      <x:c r="C36" s="86" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="D36" s="12" t="n">
+      <x:c r="D36" s="87" t="n">
         <x:v>0.79</x:v>
       </x:c>
-      <x:c r="E36" s="12" t="n">
+      <x:c r="E36" s="87" t="n">
         <x:v>4.99</x:v>
       </x:c>
-      <x:c r="F36" s="12" t="n">
+      <x:c r="F36" s="87" t="n">
         <x:v>9.99</x:v>
       </x:c>
-      <x:c r="G36" s="23" t="n">
+      <x:c r="G36" s="87" t="n">
         <x:v>7.49</x:v>
       </x:c>
-      <x:c r="H36" s="12" t="n">
+      <x:c r="H36" s="87" t="n">
         <x:v>23.99</x:v>
       </x:c>
-      <x:c r="I36" s="12" t="n">
+      <x:c r="I36" s="87" t="n">
         <x:v>47.99</x:v>
       </x:c>
-      <x:c r="J36" s="23" t="n">
+      <x:c r="J36" s="87" t="n">
         <x:f>ROUND(G36*12,2)</x:f>
         <x:v>89.88</x:v>
       </x:c>
-      <x:c r="K36" s="12" t="n">
+      <x:c r="K36" s="87" t="n">
         <x:v>2.49</x:v>
       </x:c>
-      <x:c r="L36" s="12" t="n">
+      <x:c r="L36" s="87" t="n">
         <x:v>1.29</x:v>
       </x:c>
-      <x:c r="M36" s="12" t="n">
+      <x:c r="M36" s="87" t="n">
         <x:v>1.79</x:v>
       </x:c>
-      <x:c r="N36" s="14" t="n">
+      <x:c r="N36" s="82" t="n">
         <x:f>'Pass测算'!J27</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -2887,7 +4438,7 @@
       <x:c r="F37" s="12" t="n">
         <x:v>195.99</x:v>
       </x:c>
-      <x:c r="G37" s="23" t="n">
+      <x:c r="G37" s="12" t="n">
         <x:v>146.99</x:v>
       </x:c>
       <x:c r="H37" s="12" t="n">
@@ -2896,7 +4447,7 @@
       <x:c r="I37" s="12" t="n">
         <x:v>942.99</x:v>
       </x:c>
-      <x:c r="J37" s="23" t="n">
+      <x:c r="J37" s="12" t="n">
         <x:f>ROUND(G37*12,2)</x:f>
         <x:v>1763.88</x:v>
       </x:c>
@@ -2909,7 +4460,7 @@
       <x:c r="M37" s="12" t="n">
         <x:v>33.99</x:v>
       </x:c>
-      <x:c r="N37" s="14" t="n">
+      <x:c r="N37" s="82" t="n">
         <x:f>'Pass测算'!J43</x:f>
         <x:v>8.5</x:v>
       </x:c>
@@ -2936,41 +4487,41 @@
       <x:c r="B38" s="10" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="C38" s="13" t="str">
+      <x:c r="C38" s="86" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="D38" s="12" t="n">
+      <x:c r="D38" s="87" t="n">
         <x:v>0.79</x:v>
       </x:c>
-      <x:c r="E38" s="12" t="n">
+      <x:c r="E38" s="87" t="n">
         <x:v>4.99</x:v>
       </x:c>
-      <x:c r="F38" s="12" t="n">
+      <x:c r="F38" s="87" t="n">
         <x:v>9.99</x:v>
       </x:c>
-      <x:c r="G38" s="23" t="n">
+      <x:c r="G38" s="87" t="n">
         <x:v>7.49</x:v>
       </x:c>
-      <x:c r="H38" s="12" t="n">
+      <x:c r="H38" s="87" t="n">
         <x:v>23.99</x:v>
       </x:c>
-      <x:c r="I38" s="12" t="n">
+      <x:c r="I38" s="87" t="n">
         <x:v>47.99</x:v>
       </x:c>
-      <x:c r="J38" s="23" t="n">
+      <x:c r="J38" s="87" t="n">
         <x:f>ROUND(G38*12,2)</x:f>
         <x:v>89.88</x:v>
       </x:c>
-      <x:c r="K38" s="12" t="n">
+      <x:c r="K38" s="87" t="n">
         <x:v>2.49</x:v>
       </x:c>
-      <x:c r="L38" s="12" t="n">
+      <x:c r="L38" s="87" t="n">
         <x:v>1.29</x:v>
       </x:c>
-      <x:c r="M38" s="12" t="n">
+      <x:c r="M38" s="87" t="n">
         <x:v>1.79</x:v>
       </x:c>
-      <x:c r="N38" s="14" t="n">
+      <x:c r="N38" s="82" t="n">
         <x:f>'Pass测算'!J27</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -3005,7 +4556,7 @@
       <x:c r="F39" s="21" t="n">
         <x:v>24.99</x:v>
       </x:c>
-      <x:c r="G39" s="26" t="n">
+      <x:c r="G39" s="21" t="n">
         <x:v>18.99</x:v>
       </x:c>
       <x:c r="H39" s="21" t="n">
@@ -3014,7 +4565,7 @@
       <x:c r="I39" s="21" t="n">
         <x:v>118.99</x:v>
       </x:c>
-      <x:c r="J39" s="26" t="n">
+      <x:c r="J39" s="21" t="n">
         <x:f>ROUND(G39*12,2)</x:f>
         <x:v>227.88</x:v>
       </x:c>
@@ -3066,7 +4617,7 @@
       <x:c r="F40" s="15" t="n">
         <x:v>2499</x:v>
       </x:c>
-      <x:c r="G40" s="24" t="n">
+      <x:c r="G40" s="15" t="n">
         <x:v>1899</x:v>
       </x:c>
       <x:c r="H40" s="15" t="n">
@@ -3075,7 +4626,7 @@
       <x:c r="I40" s="15" t="n">
         <x:v>11900</x:v>
       </x:c>
-      <x:c r="J40" s="24" t="n">
+      <x:c r="J40" s="15" t="n">
         <x:f>ROUND(G40*12,2)</x:f>
         <x:v>22788</x:v>
       </x:c>
@@ -3088,7 +4639,7 @@
       <x:c r="M40" s="15" t="n">
         <x:v>439</x:v>
       </x:c>
-      <x:c r="N40" s="15" t="n">
+      <x:c r="N40" s="80" t="n">
         <x:f>'Pass测算'!J52</x:f>
         <x:v>98</x:v>
       </x:c>
@@ -3127,7 +4678,7 @@
       <x:c r="F41" s="12" t="n">
         <x:v>120.99</x:v>
       </x:c>
-      <x:c r="G41" s="23" t="n">
+      <x:c r="G41" s="12" t="n">
         <x:v>89.99</x:v>
       </x:c>
       <x:c r="H41" s="12" t="n">
@@ -3136,7 +4687,7 @@
       <x:c r="I41" s="12" t="n">
         <x:v>577.99</x:v>
       </x:c>
-      <x:c r="J41" s="23" t="n">
+      <x:c r="J41" s="12" t="n">
         <x:f>ROUND(G41*12,2)</x:f>
         <x:v>1079.88</x:v>
       </x:c>
@@ -3149,7 +4700,7 @@
       <x:c r="M41" s="12" t="n">
         <x:v>20.99</x:v>
       </x:c>
-      <x:c r="N41" s="14" t="n">
+      <x:c r="N41" s="82" t="n">
         <x:f>'Pass测算'!J61</x:f>
         <x:v>4.1</x:v>
       </x:c>
@@ -3188,7 +4739,7 @@
       <x:c r="F42" s="15" t="n">
         <x:v>13900</x:v>
       </x:c>
-      <x:c r="G42" s="24" t="n">
+      <x:c r="G42" s="15" t="n">
         <x:v>10900</x:v>
       </x:c>
       <x:c r="H42" s="15" t="n">
@@ -3197,7 +4748,7 @@
       <x:c r="I42" s="15" t="n">
         <x:v>66900</x:v>
       </x:c>
-      <x:c r="J42" s="24" t="n">
+      <x:c r="J42" s="15" t="n">
         <x:f>ROUND(G42*12,2)</x:f>
         <x:v>130800</x:v>
       </x:c>
@@ -3210,7 +4761,7 @@
       <x:c r="M42" s="15" t="n">
         <x:v>2399</x:v>
       </x:c>
-      <x:c r="N42" s="15" t="n">
+      <x:c r="N42" s="80" t="n">
         <x:f>'Pass测算'!J8</x:f>
         <x:v>1100</x:v>
       </x:c>
@@ -3249,7 +4800,7 @@
       <x:c r="F43" s="12" t="n">
         <x:v>117.99</x:v>
       </x:c>
-      <x:c r="G43" s="23" t="n">
+      <x:c r="G43" s="12" t="n">
         <x:v>87.99</x:v>
       </x:c>
       <x:c r="H43" s="12" t="n">
@@ -3258,7 +4809,7 @@
       <x:c r="I43" s="12" t="n">
         <x:v>564.99</x:v>
       </x:c>
-      <x:c r="J43" s="23" t="n">
+      <x:c r="J43" s="12" t="n">
         <x:f>ROUND(G43*12,2)</x:f>
         <x:v>1055.88</x:v>
       </x:c>
@@ -3271,7 +4822,7 @@
       <x:c r="M43" s="12" t="n">
         <x:v>20.99</x:v>
       </x:c>
-      <x:c r="N43" s="15" t="n">
+      <x:c r="N43" s="80" t="n">
         <x:f>'Pass测算'!J33</x:f>
         <x:v>6</x:v>
       </x:c>
@@ -3310,7 +4861,7 @@
       <x:c r="F44" s="12" t="n">
         <x:v>197.99</x:v>
       </x:c>
-      <x:c r="G44" s="23" t="n">
+      <x:c r="G44" s="12" t="n">
         <x:v>147.99</x:v>
       </x:c>
       <x:c r="H44" s="12" t="n">
@@ -3319,7 +4870,7 @@
       <x:c r="I44" s="12" t="n">
         <x:v>947.99</x:v>
       </x:c>
-      <x:c r="J44" s="23" t="n">
+      <x:c r="J44" s="12" t="n">
         <x:f>ROUND(G44*12,2)</x:f>
         <x:v>1775.88</x:v>
       </x:c>
@@ -3332,7 +4883,7 @@
       <x:c r="M44" s="12" t="n">
         <x:v>34.99</x:v>
       </x:c>
-      <x:c r="N44" s="15" t="n">
+      <x:c r="N44" s="80" t="n">
         <x:f>'Pass测算'!J34</x:f>
         <x:v>10</x:v>
       </x:c>
@@ -3371,7 +4922,7 @@
       <x:c r="F45" s="12" t="n">
         <x:v>54.99</x:v>
       </x:c>
-      <x:c r="G45" s="23" t="n">
+      <x:c r="G45" s="12" t="n">
         <x:v>40.99</x:v>
       </x:c>
       <x:c r="H45" s="12" t="n">
@@ -3380,7 +4931,7 @@
       <x:c r="I45" s="12" t="n">
         <x:v>263.99</x:v>
       </x:c>
-      <x:c r="J45" s="23" t="n">
+      <x:c r="J45" s="12" t="n">
         <x:f>ROUND(G45*12,2)</x:f>
         <x:v>491.88</x:v>
       </x:c>
@@ -3393,7 +4944,7 @@
       <x:c r="M45" s="12" t="n">
         <x:v>9.49</x:v>
       </x:c>
-      <x:c r="N45" s="14" t="n">
+      <x:c r="N45" s="82" t="n">
         <x:f>'Pass测算'!J53</x:f>
         <x:v>2.1</x:v>
       </x:c>
@@ -3432,7 +4983,7 @@
       <x:c r="F46" s="15" t="n">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="G46" s="24" t="n">
+      <x:c r="G46" s="15" t="n">
         <x:v>339</x:v>
       </x:c>
       <x:c r="H46" s="15" t="n">
@@ -3441,7 +4992,7 @@
       <x:c r="I46" s="15" t="n">
         <x:v>2199</x:v>
       </x:c>
-      <x:c r="J46" s="24" t="n">
+      <x:c r="J46" s="15" t="n">
         <x:f>ROUND(G46*12,2)</x:f>
         <x:v>4068</x:v>
       </x:c>
@@ -3454,7 +5005,7 @@
       <x:c r="M46" s="15" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="N46" s="15" t="n">
+      <x:c r="N46" s="80" t="n">
         <x:f>'Pass测算'!J25</x:f>
         <x:v>28</x:v>
       </x:c>
@@ -3493,7 +5044,7 @@
       <x:c r="F47" s="12" t="n">
         <x:v>109.99</x:v>
       </x:c>
-      <x:c r="G47" s="23" t="n">
+      <x:c r="G47" s="12" t="n">
         <x:v>82.99</x:v>
       </x:c>
       <x:c r="H47" s="12" t="n">
@@ -3502,7 +5053,7 @@
       <x:c r="I47" s="12" t="n">
         <x:v>528.99</x:v>
       </x:c>
-      <x:c r="J47" s="23" t="n">
+      <x:c r="J47" s="12" t="n">
         <x:f>ROUND(G47*12,2)</x:f>
         <x:v>995.88</x:v>
       </x:c>
@@ -3554,7 +5105,7 @@
       <x:c r="F48" s="12" t="n">
         <x:v>7.99</x:v>
       </x:c>
-      <x:c r="G48" s="23" t="n">
+      <x:c r="G48" s="12" t="n">
         <x:v>5.99</x:v>
       </x:c>
       <x:c r="H48" s="12" t="n">
@@ -3563,7 +5114,7 @@
       <x:c r="I48" s="12" t="n">
         <x:v>37.99</x:v>
       </x:c>
-      <x:c r="J48" s="23" t="n">
+      <x:c r="J48" s="12" t="n">
         <x:f>ROUND(G48*12,2)</x:f>
         <x:v>71.88</x:v>
       </x:c>
@@ -3576,7 +5127,7 @@
       <x:c r="M48" s="12" t="n">
         <x:v>1.49</x:v>
       </x:c>
-      <x:c r="N48" s="14" t="n">
+      <x:c r="N48" s="82" t="n">
         <x:f>'Pass测算'!J9</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -3615,7 +5166,7 @@
       <x:c r="F49" s="15" t="n">
         <x:v>4599</x:v>
       </x:c>
-      <x:c r="G49" s="24" t="n">
+      <x:c r="G49" s="15" t="n">
         <x:v>3499</x:v>
       </x:c>
       <x:c r="H49" s="15" t="n">
@@ -3624,7 +5175,7 @@
       <x:c r="I49" s="15" t="n">
         <x:v>21900</x:v>
       </x:c>
-      <x:c r="J49" s="24" t="n">
+      <x:c r="J49" s="15" t="n">
         <x:f>ROUND(G49*12,2)</x:f>
         <x:v>41988</x:v>
       </x:c>
@@ -3637,7 +5188,7 @@
       <x:c r="M49" s="15" t="n">
         <x:v>809</x:v>
       </x:c>
-      <x:c r="N49" s="15" t="n">
+      <x:c r="N49" s="80" t="n">
         <x:f>'Pass测算'!J73</x:f>
         <x:v>130</x:v>
       </x:c>
@@ -3676,7 +5227,7 @@
       <x:c r="F50" s="12" t="n">
         <x:v>24.99</x:v>
       </x:c>
-      <x:c r="G50" s="23" t="n">
+      <x:c r="G50" s="12" t="n">
         <x:v>18.99</x:v>
       </x:c>
       <x:c r="H50" s="12" t="n">
@@ -3685,7 +5236,7 @@
       <x:c r="I50" s="12" t="n">
         <x:v>118.99</x:v>
       </x:c>
-      <x:c r="J50" s="23" t="n">
+      <x:c r="J50" s="12" t="n">
         <x:f>ROUND(G50*12,2)</x:f>
         <x:v>227.88</x:v>
       </x:c>
@@ -3698,7 +5249,7 @@
       <x:c r="M50" s="12" t="n">
         <x:v>4.49</x:v>
       </x:c>
-      <x:c r="N50" s="14" t="n">
+      <x:c r="N50" s="82" t="n">
         <x:f>'Pass测算'!J10</x:f>
         <x:v>1.8</x:v>
       </x:c>
@@ -3737,7 +5288,7 @@
       <x:c r="F51" s="12" t="n">
         <x:v>84.99</x:v>
       </x:c>
-      <x:c r="G51" s="23" t="n">
+      <x:c r="G51" s="12" t="n">
         <x:v>63.99</x:v>
       </x:c>
       <x:c r="H51" s="12" t="n">
@@ -3746,7 +5297,7 @@
       <x:c r="I51" s="12" t="n">
         <x:v>408.99</x:v>
       </x:c>
-      <x:c r="J51" s="23" t="n">
+      <x:c r="J51" s="12" t="n">
         <x:f>ROUND(G51*12,2)</x:f>
         <x:v>767.88</x:v>
       </x:c>
@@ -3759,7 +5310,7 @@
       <x:c r="M51" s="12" t="n">
         <x:v>14.99</x:v>
       </x:c>
-      <x:c r="N51" s="14" t="n">
+      <x:c r="N51" s="82" t="n">
         <x:f>'Pass测算'!J62</x:f>
         <x:v>2.9</x:v>
       </x:c>
@@ -3798,7 +5349,7 @@
       <x:c r="F52" s="15" t="n">
         <x:v>11900</x:v>
       </x:c>
-      <x:c r="G52" s="24" t="n">
+      <x:c r="G52" s="15" t="n">
         <x:v>8899</x:v>
       </x:c>
       <x:c r="H52" s="15" t="n">
@@ -3807,7 +5358,7 @@
       <x:c r="I52" s="15" t="n">
         <x:v>56900</x:v>
       </x:c>
-      <x:c r="J52" s="24" t="n">
+      <x:c r="J52" s="15" t="n">
         <x:f>ROUND(G52*12,2)</x:f>
         <x:v>106788</x:v>
       </x:c>
@@ -3820,7 +5371,7 @@
       <x:c r="M52" s="15" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="N52" s="15" t="n">
+      <x:c r="N52" s="80" t="n">
         <x:f>'Pass测算'!J11</x:f>
         <x:v>890</x:v>
       </x:c>
@@ -3859,7 +5410,7 @@
       <x:c r="F53" s="12" t="n">
         <x:v>89.99</x:v>
       </x:c>
-      <x:c r="G53" s="23" t="n">
+      <x:c r="G53" s="12" t="n">
         <x:v>66.99</x:v>
       </x:c>
       <x:c r="H53" s="12" t="n">
@@ -3868,7 +5419,7 @@
       <x:c r="I53" s="12" t="n">
         <x:v>431.99</x:v>
       </x:c>
-      <x:c r="J53" s="23" t="n">
+      <x:c r="J53" s="12" t="n">
         <x:f>ROUND(G53*12,2)</x:f>
         <x:v>803.88</x:v>
       </x:c>
@@ -3881,7 +5432,7 @@
       <x:c r="M53" s="12" t="n">
         <x:v>15.99</x:v>
       </x:c>
-      <x:c r="N53" s="14" t="n">
+      <x:c r="N53" s="82" t="n">
         <x:f>'Pass测算'!J79</x:f>
         <x:v>2.3</x:v>
       </x:c>
@@ -3920,7 +5471,7 @@
       <x:c r="F54" s="15" t="n">
         <x:v>969</x:v>
       </x:c>
-      <x:c r="G54" s="24" t="n">
+      <x:c r="G54" s="15" t="n">
         <x:v>719</x:v>
       </x:c>
       <x:c r="H54" s="15" t="n">
@@ -3929,7 +5480,7 @@
       <x:c r="I54" s="15" t="n">
         <x:v>4599</x:v>
       </x:c>
-      <x:c r="J54" s="24" t="n">
+      <x:c r="J54" s="15" t="n">
         <x:f>ROUND(G54*12,2)</x:f>
         <x:v>8628</x:v>
       </x:c>
@@ -3942,7 +5493,7 @@
       <x:c r="M54" s="15" t="n">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="N54" s="15" t="n">
+      <x:c r="N54" s="80" t="n">
         <x:f>'Pass测算'!J80</x:f>
         <x:v>24</x:v>
       </x:c>
@@ -3981,7 +5532,7 @@
       <x:c r="F55" s="12" t="n">
         <x:v>19.99</x:v>
       </x:c>
-      <x:c r="G55" s="23" t="n">
+      <x:c r="G55" s="12" t="n">
         <x:v>14.99</x:v>
       </x:c>
       <x:c r="H55" s="12" t="n">
@@ -3990,7 +5541,7 @@
       <x:c r="I55" s="12" t="n">
         <x:v>97.99</x:v>
       </x:c>
-      <x:c r="J55" s="23" t="n">
+      <x:c r="J55" s="12" t="n">
         <x:f>ROUND(G55*12,2)</x:f>
         <x:v>179.88</x:v>
       </x:c>
@@ -4003,7 +5554,7 @@
       <x:c r="M55" s="12" t="n">
         <x:v>3.49</x:v>
       </x:c>
-      <x:c r="N55" s="15" t="n">
+      <x:c r="N55" s="80" t="n">
         <x:f>'Pass测算'!J35</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -4042,7 +5593,7 @@
       <x:c r="F56" s="12" t="n">
         <x:v>33.99</x:v>
       </x:c>
-      <x:c r="G56" s="23" t="n">
+      <x:c r="G56" s="12" t="n">
         <x:v>25.99</x:v>
       </x:c>
       <x:c r="H56" s="12" t="n">
@@ -4051,7 +5602,7 @@
       <x:c r="I56" s="12" t="n">
         <x:v>162.99</x:v>
       </x:c>
-      <x:c r="J56" s="23" t="n">
+      <x:c r="J56" s="12" t="n">
         <x:f>ROUND(G56*12,2)</x:f>
         <x:v>311.88</x:v>
       </x:c>
@@ -4103,7 +5654,7 @@
       <x:c r="F57" s="12" t="n">
         <x:v>31.99</x:v>
       </x:c>
-      <x:c r="G57" s="23" t="n">
+      <x:c r="G57" s="12" t="n">
         <x:v>23.99</x:v>
       </x:c>
       <x:c r="H57" s="12" t="n">
@@ -4112,7 +5663,7 @@
       <x:c r="I57" s="12" t="n">
         <x:v>153.99</x:v>
       </x:c>
-      <x:c r="J57" s="23" t="n">
+      <x:c r="J57" s="12" t="n">
         <x:f>ROUND(G57*12,2)</x:f>
         <x:v>287.88</x:v>
       </x:c>
@@ -4125,7 +5676,7 @@
       <x:c r="M57" s="12" t="n">
         <x:v>5.49</x:v>
       </x:c>
-      <x:c r="N57" s="14" t="n">
+      <x:c r="N57" s="82" t="n">
         <x:f>'Pass测算'!J54</x:f>
         <x:v>1.2</x:v>
       </x:c>
@@ -4164,7 +5715,7 @@
       <x:c r="F58" s="12" t="n">
         <x:v>116.99</x:v>
       </x:c>
-      <x:c r="G58" s="23" t="n">
+      <x:c r="G58" s="12" t="n">
         <x:v>87.99</x:v>
       </x:c>
       <x:c r="H58" s="12" t="n">
@@ -4173,7 +5724,7 @@
       <x:c r="I58" s="12" t="n">
         <x:v>561.99</x:v>
       </x:c>
-      <x:c r="J58" s="23" t="n">
+      <x:c r="J58" s="12" t="n">
         <x:f>ROUND(G58*12,2)</x:f>
         <x:v>1055.88</x:v>
       </x:c>
@@ -4186,7 +5737,7 @@
       <x:c r="M58" s="12" t="n">
         <x:v>19.99</x:v>
       </x:c>
-      <x:c r="N58" s="14" t="n">
+      <x:c r="N58" s="82" t="n">
         <x:f>'Pass测算'!J26</x:f>
         <x:v>7.1</x:v>
       </x:c>
@@ -4225,7 +5776,7 @@
       <x:c r="F59" s="12" t="n">
         <x:v>26.99</x:v>
       </x:c>
-      <x:c r="G59" s="23" t="n">
+      <x:c r="G59" s="12" t="n">
         <x:v>19.99</x:v>
       </x:c>
       <x:c r="H59" s="12" t="n">
@@ -4234,7 +5785,7 @@
       <x:c r="I59" s="12" t="n">
         <x:v>127.99</x:v>
       </x:c>
-      <x:c r="J59" s="23" t="n">
+      <x:c r="J59" s="12" t="n">
         <x:f>ROUND(G59*12,2)</x:f>
         <x:v>239.88</x:v>
       </x:c>
@@ -4286,7 +5837,7 @@
       <x:c r="F60" s="12" t="n">
         <x:v>19.99</x:v>
       </x:c>
-      <x:c r="G60" s="23" t="n">
+      <x:c r="G60" s="12" t="n">
         <x:v>14.99</x:v>
       </x:c>
       <x:c r="H60" s="12" t="n">
@@ -4295,7 +5846,7 @@
       <x:c r="I60" s="12" t="n">
         <x:v>93.99</x:v>
       </x:c>
-      <x:c r="J60" s="23" t="n">
+      <x:c r="J60" s="12" t="n">
         <x:f>ROUND(G60*12,2)</x:f>
         <x:v>179.88</x:v>
       </x:c>
@@ -4308,7 +5859,7 @@
       <x:c r="M60" s="12" t="n">
         <x:v>3.49</x:v>
       </x:c>
-      <x:c r="N60" s="14" t="n">
+      <x:c r="N60" s="82" t="n">
         <x:f>'Pass测算'!J74</x:f>
         <x:v>0.53</x:v>
       </x:c>
@@ -4347,7 +5898,7 @@
       <x:c r="F61" s="12" t="n">
         <x:v>106.99</x:v>
       </x:c>
-      <x:c r="G61" s="23" t="n">
+      <x:c r="G61" s="12" t="n">
         <x:v>79.99</x:v>
       </x:c>
       <x:c r="H61" s="12" t="n">
@@ -4356,7 +5907,7 @@
       <x:c r="I61" s="12" t="n">
         <x:v>512.99</x:v>
       </x:c>
-      <x:c r="J61" s="23" t="n">
+      <x:c r="J61" s="12" t="n">
         <x:f>ROUND(G61*12,2)</x:f>
         <x:v>959.88</x:v>
       </x:c>
@@ -4369,7 +5920,7 @@
       <x:c r="M61" s="12" t="n">
         <x:v>18.99</x:v>
       </x:c>
-      <x:c r="N61" s="14" t="n">
+      <x:c r="N61" s="82" t="n">
         <x:f>'Pass测算'!J44</x:f>
         <x:v>4.6</x:v>
       </x:c>
@@ -4396,41 +5947,41 @@
       <x:c r="B62" s="10" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="C62" s="13" t="str">
+      <x:c r="C62" s="86" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="D62" s="12" t="n">
+      <x:c r="D62" s="87" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="E62" s="12" t="n">
+      <x:c r="E62" s="87" t="n">
         <x:v>6.99</x:v>
       </x:c>
-      <x:c r="F62" s="12" t="n">
+      <x:c r="F62" s="87" t="n">
         <x:v>13.99</x:v>
       </x:c>
-      <x:c r="G62" s="23" t="n">
+      <x:c r="G62" s="87" t="n">
         <x:v>10.99</x:v>
       </x:c>
-      <x:c r="H62" s="12" t="n">
+      <x:c r="H62" s="87" t="n">
         <x:v>33.99</x:v>
       </x:c>
-      <x:c r="I62" s="12" t="n">
+      <x:c r="I62" s="87" t="n">
         <x:v>66.99</x:v>
       </x:c>
-      <x:c r="J62" s="23" t="n">
+      <x:c r="J62" s="87" t="n">
         <x:f>ROUND(G62*12,2)</x:f>
         <x:v>131.88</x:v>
       </x:c>
-      <x:c r="K62" s="12" t="n">
+      <x:c r="K62" s="87" t="n">
         <x:v>3.49</x:v>
       </x:c>
-      <x:c r="L62" s="12" t="n">
+      <x:c r="L62" s="87" t="n">
         <x:v>1.79</x:v>
       </x:c>
-      <x:c r="M62" s="12" t="n">
+      <x:c r="M62" s="87" t="n">
         <x:v>2.49</x:v>
       </x:c>
-      <x:c r="N62" s="14" t="n">
+      <x:c r="N62" s="82" t="n">
         <x:f>'Pass测算'!J42</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -4453,41 +6004,41 @@
       <x:c r="B63" s="10" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="C63" s="13" t="str">
+      <x:c r="C63" s="86" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="D63" s="12" t="n">
+      <x:c r="D63" s="87" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="E63" s="12" t="n">
+      <x:c r="E63" s="87" t="n">
         <x:v>6.99</x:v>
       </x:c>
-      <x:c r="F63" s="12" t="n">
+      <x:c r="F63" s="87" t="n">
         <x:v>13.99</x:v>
       </x:c>
-      <x:c r="G63" s="23" t="n">
+      <x:c r="G63" s="87" t="n">
         <x:v>10.99</x:v>
       </x:c>
-      <x:c r="H63" s="12" t="n">
+      <x:c r="H63" s="87" t="n">
         <x:v>33.99</x:v>
       </x:c>
-      <x:c r="I63" s="12" t="n">
+      <x:c r="I63" s="87" t="n">
         <x:v>66.99</x:v>
       </x:c>
-      <x:c r="J63" s="23" t="n">
+      <x:c r="J63" s="87" t="n">
         <x:f>ROUND(G63*12,2)</x:f>
         <x:v>131.88</x:v>
       </x:c>
-      <x:c r="K63" s="12" t="n">
+      <x:c r="K63" s="87" t="n">
         <x:v>3.49</x:v>
       </x:c>
-      <x:c r="L63" s="12" t="n">
+      <x:c r="L63" s="87" t="n">
         <x:v>1.79</x:v>
       </x:c>
-      <x:c r="M63" s="12" t="n">
+      <x:c r="M63" s="87" t="n">
         <x:v>2.49</x:v>
       </x:c>
-      <x:c r="N63" s="14" t="n">
+      <x:c r="N63" s="82" t="n">
         <x:f>'Pass测算'!J42</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -4522,7 +6073,7 @@
       <x:c r="F64" s="12" t="n">
         <x:v>19.99</x:v>
       </x:c>
-      <x:c r="G64" s="23" t="n">
+      <x:c r="G64" s="12" t="n">
         <x:v>14.99</x:v>
       </x:c>
       <x:c r="H64" s="12" t="n">
@@ -4531,7 +6082,7 @@
       <x:c r="I64" s="12" t="n">
         <x:v>95.99</x:v>
       </x:c>
-      <x:c r="J64" s="23" t="n">
+      <x:c r="J64" s="12" t="n">
         <x:f>ROUND(G64*12,2)</x:f>
         <x:v>179.88</x:v>
       </x:c>
@@ -4544,7 +6095,7 @@
       <x:c r="M64" s="12" t="n">
         <x:v>3.49</x:v>
       </x:c>
-      <x:c r="N64" s="14" t="n">
+      <x:c r="N64" s="82" t="n">
         <x:f>'Pass测算'!J66</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -4583,7 +6134,7 @@
       <x:c r="F65" s="12" t="n">
         <x:v>48.99</x:v>
       </x:c>
-      <x:c r="G65" s="23" t="n">
+      <x:c r="G65" s="12" t="n">
         <x:v>35.99</x:v>
       </x:c>
       <x:c r="H65" s="12" t="n">
@@ -4592,7 +6143,7 @@
       <x:c r="I65" s="12" t="n">
         <x:v>232.99</x:v>
       </x:c>
-      <x:c r="J65" s="23" t="n">
+      <x:c r="J65" s="12" t="n">
         <x:f>ROUND(G65*12,2)</x:f>
         <x:v>431.88</x:v>
       </x:c>
@@ -4605,7 +6156,7 @@
       <x:c r="M65" s="12" t="n">
         <x:v>8.49</x:v>
       </x:c>
-      <x:c r="N65" s="14" t="n">
+      <x:c r="N65" s="82" t="n">
         <x:f>'Pass测算'!J63</x:f>
         <x:v>1.7</x:v>
       </x:c>
@@ -4644,7 +6195,7 @@
       <x:c r="F66" s="12" t="n">
         <x:v>22.99</x:v>
       </x:c>
-      <x:c r="G66" s="23" t="n">
+      <x:c r="G66" s="12" t="n">
         <x:v>16.99</x:v>
       </x:c>
       <x:c r="H66" s="12" t="n">
@@ -4653,7 +6204,7 @@
       <x:c r="I66" s="12" t="n">
         <x:v>110.99</x:v>
       </x:c>
-      <x:c r="J66" s="23" t="n">
+      <x:c r="J66" s="12" t="n">
         <x:f>ROUND(G66*12,2)</x:f>
         <x:v>203.88</x:v>
       </x:c>
@@ -4705,7 +6256,7 @@
       <x:c r="F67" s="15" t="n">
         <x:v>3299</x:v>
       </x:c>
-      <x:c r="G67" s="24" t="n">
+      <x:c r="G67" s="15" t="n">
         <x:v>2499</x:v>
       </x:c>
       <x:c r="H67" s="15" t="n">
@@ -4714,7 +6265,7 @@
       <x:c r="I67" s="15" t="n">
         <x:v>15900</x:v>
       </x:c>
-      <x:c r="J67" s="24" t="n">
+      <x:c r="J67" s="15" t="n">
         <x:f>ROUND(G67*12,2)</x:f>
         <x:v>29988</x:v>
       </x:c>
@@ -4727,7 +6278,7 @@
       <x:c r="M67" s="15" t="n">
         <x:v>579</x:v>
       </x:c>
-      <x:c r="N67" s="15" t="n">
+      <x:c r="N67" s="80" t="n">
         <x:f>'Pass测算'!J28</x:f>
         <x:v>210</x:v>
       </x:c>
@@ -4766,7 +6317,7 @@
       <x:c r="F68" s="15" t="n">
         <x:v>20900</x:v>
       </x:c>
-      <x:c r="G68" s="24" t="n">
+      <x:c r="G68" s="15" t="n">
         <x:v>15900</x:v>
       </x:c>
       <x:c r="H68" s="15" t="n">
@@ -4775,7 +6326,7 @@
       <x:c r="I68" s="15" t="n">
         <x:v>99000</x:v>
       </x:c>
-      <x:c r="J68" s="24" t="n">
+      <x:c r="J68" s="15" t="n">
         <x:f>ROUND(G68*12,2)</x:f>
         <x:v>190800</x:v>
       </x:c>
@@ -4788,7 +6339,7 @@
       <x:c r="M68" s="15" t="n">
         <x:v>3699</x:v>
       </x:c>
-      <x:c r="N68" s="15" t="n">
+      <x:c r="N68" s="80" t="n">
         <x:f>'Pass测算'!J12</x:f>
         <x:v>1700</x:v>
       </x:c>
@@ -4827,7 +6378,7 @@
       <x:c r="F69" s="15" t="n">
         <x:v>31900</x:v>
       </x:c>
-      <x:c r="G69" s="24" t="n">
+      <x:c r="G69" s="15" t="n">
         <x:v>23900</x:v>
       </x:c>
       <x:c r="H69" s="15" t="n">
@@ -4836,7 +6387,7 @@
       <x:c r="I69" s="15" t="n">
         <x:v>152900</x:v>
       </x:c>
-      <x:c r="J69" s="24" t="n">
+      <x:c r="J69" s="15" t="n">
         <x:f>ROUND(G69*12,2)</x:f>
         <x:v>286800</x:v>
       </x:c>
@@ -4849,7 +6400,7 @@
       <x:c r="M69" s="15" t="n">
         <x:v>5599</x:v>
       </x:c>
-      <x:c r="N69" s="15" t="n">
+      <x:c r="N69" s="80" t="n">
         <x:f>'Pass测算'!J13</x:f>
         <x:v>2400</x:v>
       </x:c>
@@ -4876,41 +6427,41 @@
       <x:c r="B70" s="10" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="C70" s="13" t="str">
+      <x:c r="C70" s="86" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="D70" s="12" t="n">
+      <x:c r="D70" s="87" t="n">
         <x:v>0.59</x:v>
       </x:c>
-      <x:c r="E70" s="12" t="n">
+      <x:c r="E70" s="87" t="n">
         <x:v>3.99</x:v>
       </x:c>
-      <x:c r="F70" s="12" t="n">
+      <x:c r="F70" s="87" t="n">
         <x:v>7.99</x:v>
       </x:c>
-      <x:c r="G70" s="23" t="n">
+      <x:c r="G70" s="87" t="n">
         <x:v>5.99</x:v>
       </x:c>
-      <x:c r="H70" s="12" t="n">
+      <x:c r="H70" s="87" t="n">
         <x:v>18.99</x:v>
       </x:c>
-      <x:c r="I70" s="12" t="n">
+      <x:c r="I70" s="87" t="n">
         <x:v>37.99</x:v>
       </x:c>
-      <x:c r="J70" s="23" t="n">
+      <x:c r="J70" s="87" t="n">
         <x:f>ROUND(G70*12,2)</x:f>
         <x:v>71.88</x:v>
       </x:c>
-      <x:c r="K70" s="12" t="n">
+      <x:c r="K70" s="87" t="n">
         <x:v>1.99</x:v>
       </x:c>
-      <x:c r="L70" s="12" t="n">
+      <x:c r="L70" s="87" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="M70" s="12" t="n">
+      <x:c r="M70" s="87" t="n">
         <x:v>1.49</x:v>
       </x:c>
-      <x:c r="N70" s="14" t="n">
+      <x:c r="N70" s="82" t="n">
         <x:f>'Pass测算'!J9</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -4945,7 +6496,7 @@
       <x:c r="F71" s="15" t="n">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="G71" s="24" t="n">
+      <x:c r="G71" s="15" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="H71" s="15" t="n">
@@ -4954,7 +6505,7 @@
       <x:c r="I71" s="15" t="n">
         <x:v>769</x:v>
       </x:c>
-      <x:c r="J71" s="24" t="n">
+      <x:c r="J71" s="15" t="n">
         <x:f>ROUND(G71*12,2)</x:f>
         <x:v>1428</x:v>
       </x:c>
@@ -4967,7 +6518,7 @@
       <x:c r="M71" s="15" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="N71" s="15" t="n">
+      <x:c r="N71" s="80" t="n">
         <x:f>'Pass测算'!J14</x:f>
         <x:v>12</x:v>
       </x:c>
@@ -5006,7 +6557,7 @@
       <x:c r="F72" s="15" t="n">
         <x:v>519</x:v>
       </x:c>
-      <x:c r="G72" s="24" t="n">
+      <x:c r="G72" s="15" t="n">
         <x:v>389</x:v>
       </x:c>
       <x:c r="H72" s="15" t="n">
@@ -5015,7 +6566,7 @@
       <x:c r="I72" s="15" t="n">
         <x:v>2499</x:v>
       </x:c>
-      <x:c r="J72" s="24" t="n">
+      <x:c r="J72" s="15" t="n">
         <x:f>ROUND(G72*12,2)</x:f>
         <x:v>4668</x:v>
       </x:c>
@@ -5028,7 +6579,7 @@
       <x:c r="M72" s="15" t="n">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="N72" s="15" t="n">
+      <x:c r="N72" s="80" t="n">
         <x:f>'Pass测算'!J15</x:f>
         <x:v>39</x:v>
       </x:c>
@@ -5067,7 +6618,7 @@
       <x:c r="F73" s="15" t="n">
         <x:v>1299</x:v>
       </x:c>
-      <x:c r="G73" s="24" t="n">
+      <x:c r="G73" s="15" t="n">
         <x:v>979</x:v>
       </x:c>
       <x:c r="H73" s="15" t="n">
@@ -5076,7 +6627,7 @@
       <x:c r="I73" s="15" t="n">
         <x:v>6299</x:v>
       </x:c>
-      <x:c r="J73" s="24" t="n">
+      <x:c r="J73" s="15" t="n">
         <x:f>ROUND(G73*12,2)</x:f>
         <x:v>11748</x:v>
       </x:c>
@@ -5089,7 +6640,7 @@
       <x:c r="M73" s="15" t="n">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="N73" s="15" t="n">
+      <x:c r="N73" s="80" t="n">
         <x:f>'Pass测算'!J55</x:f>
         <x:v>49</x:v>
       </x:c>
@@ -5128,7 +6679,7 @@
       <x:c r="F74" s="12" t="n">
         <x:v>43.99</x:v>
       </x:c>
-      <x:c r="G74" s="23" t="n">
+      <x:c r="G74" s="12" t="n">
         <x:v>32.99</x:v>
       </x:c>
       <x:c r="H74" s="12" t="n">
@@ -5137,7 +6688,7 @@
       <x:c r="I74" s="12" t="n">
         <x:v>210.99</x:v>
       </x:c>
-      <x:c r="J74" s="23" t="n">
+      <x:c r="J74" s="12" t="n">
         <x:f>ROUND(G74*12,2)</x:f>
         <x:v>395.88</x:v>
       </x:c>
@@ -5150,7 +6701,7 @@
       <x:c r="M74" s="12" t="n">
         <x:v>7.49</x:v>
       </x:c>
-      <x:c r="N74" s="14" t="n">
+      <x:c r="N74" s="82" t="n">
         <x:f>'Pass测算'!J75</x:f>
         <x:v>1.3</x:v>
       </x:c>
@@ -5189,7 +6740,7 @@
       <x:c r="F75" s="12" t="n">
         <x:v>27.99</x:v>
       </x:c>
-      <x:c r="G75" s="23" t="n">
+      <x:c r="G75" s="12" t="n">
         <x:v>20.99</x:v>
       </x:c>
       <x:c r="H75" s="12" t="n">
@@ -5198,7 +6749,7 @@
       <x:c r="I75" s="12" t="n">
         <x:v>136.99</x:v>
       </x:c>
-      <x:c r="J75" s="23" t="n">
+      <x:c r="J75" s="12" t="n">
         <x:f>ROUND(G75*12,2)</x:f>
         <x:v>251.88</x:v>
       </x:c>
@@ -5250,7 +6801,7 @@
       <x:c r="F76" s="12" t="n">
         <x:v>39.99</x:v>
       </x:c>
-      <x:c r="G76" s="23" t="n">
+      <x:c r="G76" s="12" t="n">
         <x:v>29.99</x:v>
       </x:c>
       <x:c r="H76" s="12" t="n">
@@ -5259,7 +6810,7 @@
       <x:c r="I76" s="12" t="n">
         <x:v>191.99</x:v>
       </x:c>
-      <x:c r="J76" s="23" t="n">
+      <x:c r="J76" s="12" t="n">
         <x:f>ROUND(G76*12,2)</x:f>
         <x:v>359.88</x:v>
       </x:c>
@@ -5311,7 +6862,7 @@
       <x:c r="F77" s="12" t="n">
         <x:v>27.99</x:v>
       </x:c>
-      <x:c r="G77" s="23" t="n">
+      <x:c r="G77" s="12" t="n">
         <x:v>20.99</x:v>
       </x:c>
       <x:c r="H77" s="12" t="n">
@@ -5320,7 +6871,7 @@
       <x:c r="I77" s="12" t="n">
         <x:v>134.99</x:v>
       </x:c>
-      <x:c r="J77" s="23" t="n">
+      <x:c r="J77" s="12" t="n">
         <x:f>ROUND(G77*12,2)</x:f>
         <x:v>251.88</x:v>
       </x:c>
@@ -5333,7 +6884,7 @@
       <x:c r="M77" s="12" t="n">
         <x:v>4.99</x:v>
       </x:c>
-      <x:c r="N77" s="14" t="n">
+      <x:c r="N77" s="82" t="n">
         <x:f>'Pass测算'!J76</x:f>
         <x:v>0.77</x:v>
       </x:c>
@@ -5372,7 +6923,7 @@
       <x:c r="F78" s="15" t="n">
         <x:v>40900</x:v>
       </x:c>
-      <x:c r="G78" s="24" t="n">
+      <x:c r="G78" s="15" t="n">
         <x:v>30900</x:v>
       </x:c>
       <x:c r="H78" s="15" t="n">
@@ -5381,7 +6932,7 @@
       <x:c r="I78" s="15" t="n">
         <x:v>199000</x:v>
       </x:c>
-      <x:c r="J78" s="24" t="n">
+      <x:c r="J78" s="15" t="n">
         <x:f>ROUND(G78*12,2)</x:f>
         <x:v>370800</x:v>
       </x:c>
@@ -5394,7 +6945,7 @@
       <x:c r="M78" s="15" t="n">
         <x:v>7099</x:v>
       </x:c>
-      <x:c r="N78" s="15" t="n">
+      <x:c r="N78" s="80" t="n">
         <x:f>'Pass测算'!J29</x:f>
         <x:v>2400</x:v>
       </x:c>
@@ -5433,7 +6984,7 @@
       <x:c r="F79" s="15" t="n">
         <x:v>4699</x:v>
       </x:c>
-      <x:c r="G79" s="24" t="n">
+      <x:c r="G79" s="15" t="n">
         <x:v>3499</x:v>
       </x:c>
       <x:c r="H79" s="15" t="n">
@@ -5442,7 +6993,7 @@
       <x:c r="I79" s="15" t="n">
         <x:v>22900</x:v>
       </x:c>
-      <x:c r="J79" s="24" t="n">
+      <x:c r="J79" s="15" t="n">
         <x:f>ROUND(G79*12,2)</x:f>
         <x:v>41988</x:v>
       </x:c>
@@ -5455,7 +7006,7 @@
       <x:c r="M79" s="15" t="n">
         <x:v>819</x:v>
       </x:c>
-      <x:c r="N79" s="15" t="n">
+      <x:c r="N79" s="80" t="n">
         <x:f>'Pass测算'!J16</x:f>
         <x:v>350</x:v>
       </x:c>
@@ -5494,7 +7045,7 @@
       <x:c r="F80" s="15" t="n">
         <x:v>17900</x:v>
       </x:c>
-      <x:c r="G80" s="24" t="n">
+      <x:c r="G80" s="15" t="n">
         <x:v>12900</x:v>
       </x:c>
       <x:c r="H80" s="15" t="n">
@@ -5503,7 +7054,7 @@
       <x:c r="I80" s="15" t="n">
         <x:v>84900</x:v>
       </x:c>
-      <x:c r="J80" s="24" t="n">
+      <x:c r="J80" s="15" t="n">
         <x:f>ROUND(G80*12,2)</x:f>
         <x:v>154800</x:v>
       </x:c>
@@ -5516,7 +7067,7 @@
       <x:c r="M80" s="15" t="n">
         <x:v>3099</x:v>
       </x:c>
-      <x:c r="N80" s="15" t="n">
+      <x:c r="N80" s="80" t="n">
         <x:f>'Pass测算'!J64</x:f>
         <x:v>590</x:v>
       </x:c>
@@ -5555,7 +7106,7 @@
       <x:c r="F81" s="15" t="n">
         <x:v>9099</x:v>
       </x:c>
-      <x:c r="G81" s="24" t="n">
+      <x:c r="G81" s="15" t="n">
         <x:v>6799</x:v>
       </x:c>
       <x:c r="H81" s="15" t="n">
@@ -5564,7 +7115,7 @@
       <x:c r="I81" s="15" t="n">
         <x:v>43900</x:v>
       </x:c>
-      <x:c r="J81" s="24" t="n">
+      <x:c r="J81" s="15" t="n">
         <x:f>ROUND(G81*12,2)</x:f>
         <x:v>81588</x:v>
       </x:c>
@@ -5577,7 +7128,7 @@
       <x:c r="M81" s="15" t="n">
         <x:v>1599</x:v>
       </x:c>
-      <x:c r="N81" s="15" t="n">
+      <x:c r="N81" s="80" t="n">
         <x:f>'Pass测算'!J67</x:f>
         <x:v>280</x:v>
       </x:c>
@@ -5616,7 +7167,7 @@
       <x:c r="F82" s="12" t="n">
         <x:v>17.99</x:v>
       </x:c>
-      <x:c r="G82" s="23" t="n">
+      <x:c r="G82" s="12" t="n">
         <x:v>12.99</x:v>
       </x:c>
       <x:c r="H82" s="12" t="n">
@@ -5625,7 +7176,7 @@
       <x:c r="I82" s="12" t="n">
         <x:v>84.99</x:v>
       </x:c>
-      <x:c r="J82" s="23" t="n">
+      <x:c r="J82" s="12" t="n">
         <x:f>ROUND(G82*12,2)</x:f>
         <x:v>155.88</x:v>
       </x:c>
@@ -5638,7 +7189,7 @@
       <x:c r="M82" s="12" t="n">
         <x:v>2.99</x:v>
       </x:c>
-      <x:c r="N82" s="14" t="n">
+      <x:c r="N82" s="82" t="n">
         <x:f>'Pass测算'!J68</x:f>
         <x:v>0.53</x:v>
       </x:c>
@@ -5677,7 +7228,7 @@
       <x:c r="F83" s="12" t="n">
         <x:v>13.99</x:v>
       </x:c>
-      <x:c r="G83" s="23" t="n">
+      <x:c r="G83" s="12" t="n">
         <x:v>10.99</x:v>
       </x:c>
       <x:c r="H83" s="12" t="n">
@@ -5686,7 +7237,7 @@
       <x:c r="I83" s="12" t="n">
         <x:v>66.99</x:v>
       </x:c>
-      <x:c r="J83" s="23" t="n">
+      <x:c r="J83" s="12" t="n">
         <x:f>ROUND(G83*12,2)</x:f>
         <x:v>131.88</x:v>
       </x:c>
@@ -5699,7 +7250,7 @@
       <x:c r="M83" s="12" t="n">
         <x:v>2.49</x:v>
       </x:c>
-      <x:c r="N83" s="14" t="n">
+      <x:c r="N83" s="82" t="n">
         <x:f>'Pass测算'!J42</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -5738,7 +7289,7 @@
       <x:c r="F84" s="12" t="n">
         <x:v>27.99</x:v>
       </x:c>
-      <x:c r="G84" s="23" t="n">
+      <x:c r="G84" s="12" t="n">
         <x:v>20.99</x:v>
       </x:c>
       <x:c r="H84" s="12" t="n">
@@ -5747,7 +7298,7 @@
       <x:c r="I84" s="12" t="n">
         <x:v>136.99</x:v>
       </x:c>
-      <x:c r="J84" s="23" t="n">
+      <x:c r="J84" s="12" t="n">
         <x:f>ROUND(G84*12,2)</x:f>
         <x:v>251.88</x:v>
       </x:c>
@@ -5799,7 +7350,7 @@
       <x:c r="F85" s="15" t="n">
         <x:v>8199</x:v>
       </x:c>
-      <x:c r="G85" s="24" t="n">
+      <x:c r="G85" s="15" t="n">
         <x:v>6099</x:v>
       </x:c>
       <x:c r="H85" s="15" t="n">
@@ -5808,7 +7359,7 @@
       <x:c r="I85" s="15" t="n">
         <x:v>38900</x:v>
       </x:c>
-      <x:c r="J85" s="24" t="n">
+      <x:c r="J85" s="15" t="n">
         <x:f>ROUND(G85*12,2)</x:f>
         <x:v>73188</x:v>
       </x:c>
@@ -5821,7 +7372,7 @@
       <x:c r="M85" s="15" t="n">
         <x:v>1399</x:v>
       </x:c>
-      <x:c r="N85" s="15" t="n">
+      <x:c r="N85" s="80" t="n">
         <x:f>'Pass测算'!J45</x:f>
         <x:v>350</x:v>
       </x:c>
@@ -5860,7 +7411,7 @@
       <x:c r="F86" s="12" t="n">
         <x:v>35.99</x:v>
       </x:c>
-      <x:c r="G86" s="23" t="n">
+      <x:c r="G86" s="12" t="n">
         <x:v>26.99</x:v>
       </x:c>
       <x:c r="H86" s="12" t="n">
@@ -5869,7 +7420,7 @@
       <x:c r="I86" s="12" t="n">
         <x:v>173.99</x:v>
       </x:c>
-      <x:c r="J86" s="23" t="n">
+      <x:c r="J86" s="12" t="n">
         <x:f>ROUND(G86*12,2)</x:f>
         <x:v>323.88</x:v>
       </x:c>
@@ -5882,7 +7433,7 @@
       <x:c r="M86" s="12" t="n">
         <x:v>6.49</x:v>
       </x:c>
-      <x:c r="N86" s="14" t="n">
+      <x:c r="N86" s="82" t="n">
         <x:f>'Pass测算'!J46</x:f>
         <x:v>1.6</x:v>
       </x:c>
@@ -5921,7 +7472,7 @@
       <x:c r="F87" s="15" t="n">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="G87" s="24" t="n">
+      <x:c r="G87" s="15" t="n">
         <x:v>239</x:v>
       </x:c>
       <x:c r="H87" s="15" t="n">
@@ -5930,7 +7481,7 @@
       <x:c r="I87" s="15" t="n">
         <x:v>1499</x:v>
       </x:c>
-      <x:c r="J87" s="24" t="n">
+      <x:c r="J87" s="15" t="n">
         <x:f>ROUND(G87*12,2)</x:f>
         <x:v>2868</x:v>
       </x:c>
@@ -5943,7 +7494,7 @@
       <x:c r="M87" s="15" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="N87" s="15" t="n">
+      <x:c r="N87" s="80" t="n">
         <x:f>'Pass测算'!J37</x:f>
         <x:v>16</x:v>
       </x:c>
@@ -5982,7 +7533,7 @@
       <x:c r="F88" s="15" t="n">
         <x:v>6499</x:v>
       </x:c>
-      <x:c r="G88" s="24" t="n">
+      <x:c r="G88" s="15" t="n">
         <x:v>4799</x:v>
       </x:c>
       <x:c r="H88" s="15" t="n">
@@ -5991,7 +7542,7 @@
       <x:c r="I88" s="15" t="n">
         <x:v>30900</x:v>
       </x:c>
-      <x:c r="J88" s="24" t="n">
+      <x:c r="J88" s="15" t="n">
         <x:f>ROUND(G88*12,2)</x:f>
         <x:v>57588</x:v>
       </x:c>
@@ -6004,7 +7555,7 @@
       <x:c r="M88" s="15" t="n">
         <x:v>1099</x:v>
       </x:c>
-      <x:c r="N88" s="15" t="n">
+      <x:c r="N88" s="80" t="n">
         <x:f>'Pass测算'!J69</x:f>
         <x:v>200</x:v>
       </x:c>
@@ -6043,7 +7594,7 @@
       <x:c r="F89" s="15" t="n">
         <x:v>5799</x:v>
       </x:c>
-      <x:c r="G89" s="24" t="n">
+      <x:c r="G89" s="15" t="n">
         <x:v>4399</x:v>
       </x:c>
       <x:c r="H89" s="15" t="n">
@@ -6052,7 +7603,7 @@
       <x:c r="I89" s="15" t="n">
         <x:v>27900</x:v>
       </x:c>
-      <x:c r="J89" s="24" t="n">
+      <x:c r="J89" s="15" t="n">
         <x:f>ROUND(G89*12,2)</x:f>
         <x:v>52788</x:v>
       </x:c>
@@ -6065,7 +7616,7 @@
       <x:c r="M89" s="15" t="n">
         <x:v>999</x:v>
       </x:c>
-      <x:c r="N89" s="15" t="n">
+      <x:c r="N89" s="80" t="n">
         <x:f>'Pass测算'!J30</x:f>
         <x:v>350</x:v>
       </x:c>
@@ -6104,7 +7655,7 @@
       <x:c r="F90" s="15" t="n">
         <x:v>7199</x:v>
       </x:c>
-      <x:c r="G90" s="24" t="n">
+      <x:c r="G90" s="15" t="n">
         <x:v>5399</x:v>
       </x:c>
       <x:c r="H90" s="15" t="n">
@@ -6113,7 +7664,7 @@
       <x:c r="I90" s="15" t="n">
         <x:v>34900</x:v>
       </x:c>
-      <x:c r="J90" s="24" t="n">
+      <x:c r="J90" s="15" t="n">
         <x:f>ROUND(G90*12,2)</x:f>
         <x:v>64788</x:v>
       </x:c>
@@ -6126,7 +7677,7 @@
       <x:c r="M90" s="15" t="n">
         <x:v>1299</x:v>
       </x:c>
-      <x:c r="N90" s="15" t="n">
+      <x:c r="N90" s="80" t="n">
         <x:f>'Pass测算'!J56</x:f>
         <x:v>280</x:v>
       </x:c>
@@ -6153,41 +7704,41 @@
       <x:c r="B91" s="10" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="C91" s="13" t="str">
+      <x:c r="C91" s="86" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="D91" s="12" t="n">
+      <x:c r="D91" s="81" t="n">
         <x:v>1.95</x:v>
       </x:c>
-      <x:c r="E91" s="12" t="n">
+      <x:c r="E91" s="87" t="n">
         <x:v>12.99</x:v>
       </x:c>
-      <x:c r="F91" s="12" t="n">
+      <x:c r="F91" s="87" t="n">
         <x:v>25.99</x:v>
       </x:c>
-      <x:c r="G91" s="23" t="n">
+      <x:c r="G91" s="87" t="n">
         <x:v>19.49</x:v>
       </x:c>
-      <x:c r="H91" s="12" t="n">
+      <x:c r="H91" s="81" t="n">
         <x:v>62.3</x:v>
       </x:c>
-      <x:c r="I91" s="12" t="n">
+      <x:c r="I91" s="81" t="n">
         <x:v>124.7</x:v>
       </x:c>
-      <x:c r="J91" s="23" t="n">
+      <x:c r="J91" s="87" t="n">
         <x:f>ROUND(G91*12,2)</x:f>
         <x:v>233.88</x:v>
       </x:c>
-      <x:c r="K91" s="12" t="n">
+      <x:c r="K91" s="87" t="n">
         <x:v>6.49</x:v>
       </x:c>
-      <x:c r="L91" s="12" t="n">
+      <x:c r="L91" s="81" t="n">
         <x:v>3.25</x:v>
       </x:c>
-      <x:c r="M91" s="12" t="n">
+      <x:c r="M91" s="81" t="n">
         <x:v>4.55</x:v>
       </x:c>
-      <x:c r="N91" s="14" t="n">
+      <x:c r="N91" s="88" t="n">
         <x:f>'Pass测算'!J85</x:f>
         <x:v>0.65</x:v>
       </x:c>
@@ -6222,7 +7773,7 @@
       <x:c r="F92" s="15" t="n">
         <x:v>179000</x:v>
       </x:c>
-      <x:c r="G92" s="24" t="n">
+      <x:c r="G92" s="15" t="n">
         <x:v>129000</x:v>
       </x:c>
       <x:c r="H92" s="15" t="n">
@@ -6231,7 +7782,7 @@
       <x:c r="I92" s="15" t="n">
         <x:v>859000</x:v>
       </x:c>
-      <x:c r="J92" s="24" t="n">
+      <x:c r="J92" s="15" t="n">
         <x:f>ROUND(G92*12,2)</x:f>
         <x:v>1548000</x:v>
       </x:c>
@@ -6244,7 +7795,7 @@
       <x:c r="M92" s="15" t="n">
         <x:v>30900</x:v>
       </x:c>
-      <x:c r="N92" s="15" t="n">
+      <x:c r="N92" s="80" t="n">
         <x:f>'Pass测算'!J17</x:f>
         <x:v>13400</x:v>
       </x:c>
@@ -6283,7 +7834,7 @@
       <x:c r="F93" s="12" t="n">
         <x:v>19.99</x:v>
       </x:c>
-      <x:c r="G93" s="23" t="n">
+      <x:c r="G93" s="12" t="n">
         <x:v>14.99</x:v>
       </x:c>
       <x:c r="H93" s="12" t="n">
@@ -6292,7 +7843,7 @@
       <x:c r="I93" s="12" t="n">
         <x:v>93.99</x:v>
       </x:c>
-      <x:c r="J93" s="23" t="n">
+      <x:c r="J93" s="12" t="n">
         <x:f>ROUND(G93*12,2)</x:f>
         <x:v>179.88</x:v>
       </x:c>
@@ -6305,7 +7856,7 @@
       <x:c r="M93" s="12" t="n">
         <x:v>3.49</x:v>
       </x:c>
-      <x:c r="N93" s="14" t="n">
+      <x:c r="N93" s="82" t="n">
         <x:f>'Pass测算'!J74</x:f>
         <x:v>0.53</x:v>
       </x:c>
@@ -6344,7 +7895,7 @@
       <x:c r="F94" s="15" t="n">
         <x:v>1290000</x:v>
       </x:c>
-      <x:c r="G94" s="24" t="n">
+      <x:c r="G94" s="15" t="n">
         <x:v>939000</x:v>
       </x:c>
       <x:c r="H94" s="15" t="n">
@@ -6353,7 +7904,7 @@
       <x:c r="I94" s="15" t="n">
         <x:v>6090000</x:v>
       </x:c>
-      <x:c r="J94" s="24" t="n">
+      <x:c r="J94" s="15" t="n">
         <x:f>ROUND(G94*12,2)</x:f>
         <x:v>11268000</x:v>
       </x:c>
@@ -6366,7 +7917,7 @@
       <x:c r="M94" s="15" t="n">
         <x:v>219000</x:v>
       </x:c>
-      <x:c r="N94" s="15" t="n">
+      <x:c r="N94" s="80" t="n">
         <x:f>'Pass测算'!J47</x:f>
         <x:v>54000</x:v>
       </x:c>
@@ -6405,7 +7956,7 @@
       <x:c r="F95" s="15" t="n">
         <x:v>1399</x:v>
       </x:c>
-      <x:c r="G95" s="24" t="n">
+      <x:c r="G95" s="15" t="n">
         <x:v>999</x:v>
       </x:c>
       <x:c r="H95" s="15" t="n">
@@ -6414,7 +7965,7 @@
       <x:c r="I95" s="15" t="n">
         <x:v>6599</x:v>
       </x:c>
-      <x:c r="J95" s="24" t="n">
+      <x:c r="J95" s="15" t="n">
         <x:f>ROUND(G95*12,2)</x:f>
         <x:v>11988</x:v>
       </x:c>
@@ -6427,7 +7978,7 @@
       <x:c r="M95" s="15" t="n">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="N95" s="15" t="n">
+      <x:c r="N95" s="80" t="n">
         <x:f>'Pass测算'!J18</x:f>
         <x:v>110</x:v>
       </x:c>
@@ -6466,7 +8017,7 @@
       <x:c r="F96" s="12" t="n">
         <x:v>33.99</x:v>
       </x:c>
-      <x:c r="G96" s="23" t="n">
+      <x:c r="G96" s="12" t="n">
         <x:v>24.99</x:v>
       </x:c>
       <x:c r="H96" s="12" t="n">
@@ -6475,7 +8026,7 @@
       <x:c r="I96" s="12" t="n">
         <x:v>161.99</x:v>
       </x:c>
-      <x:c r="J96" s="23" t="n">
+      <x:c r="J96" s="12" t="n">
         <x:f>ROUND(G96*12,2)</x:f>
         <x:v>299.88</x:v>
       </x:c>
@@ -6527,7 +8078,7 @@
       <x:c r="F97" s="12" t="n">
         <x:v>277.99</x:v>
       </x:c>
-      <x:c r="G97" s="23" t="n">
+      <x:c r="G97" s="12" t="n">
         <x:v>208.99</x:v>
       </x:c>
       <x:c r="H97" s="12" t="n">
@@ -6536,7 +8087,7 @@
       <x:c r="I97" s="12" t="n">
         <x:v>1333.99</x:v>
       </x:c>
-      <x:c r="J97" s="23" t="n">
+      <x:c r="J97" s="12" t="n">
         <x:f>ROUND(G97*12,2)</x:f>
         <x:v>2507.88</x:v>
       </x:c>
@@ -6549,7 +8100,7 @@
       <x:c r="M97" s="12" t="n">
         <x:v>48.99</x:v>
       </x:c>
-      <x:c r="N97" s="14" t="n">
+      <x:c r="N97" s="82" t="n">
         <x:f>'Pass测算'!J65</x:f>
         <x:v>9.3</x:v>
       </x:c>
@@ -6588,7 +8139,7 @@
       <x:c r="F98" s="12" t="n">
         <x:v>250.99</x:v>
       </x:c>
-      <x:c r="G98" s="23" t="n">
+      <x:c r="G98" s="12" t="n">
         <x:v>187.99</x:v>
       </x:c>
       <x:c r="H98" s="12" t="n">
@@ -6597,7 +8148,7 @@
       <x:c r="I98" s="12" t="n">
         <x:v>1202.99</x:v>
       </x:c>
-      <x:c r="J98" s="23" t="n">
+      <x:c r="J98" s="12" t="n">
         <x:f>ROUND(G98*12,2)</x:f>
         <x:v>2255.88</x:v>
       </x:c>
@@ -6610,7 +8161,7 @@
       <x:c r="M98" s="12" t="n">
         <x:v>43.99</x:v>
       </x:c>
-      <x:c r="N98" s="15" t="n">
+      <x:c r="N98" s="80" t="n">
         <x:f>'Pass测算'!J48</x:f>
         <x:v>11</x:v>
       </x:c>
@@ -6649,7 +8200,7 @@
       <x:c r="F99" s="15" t="n">
         <x:v>42900</x:v>
       </x:c>
-      <x:c r="G99" s="24" t="n">
+      <x:c r="G99" s="15" t="n">
         <x:v>32900</x:v>
       </x:c>
       <x:c r="H99" s="15" t="n">
@@ -6658,7 +8209,7 @@
       <x:c r="I99" s="15" t="n">
         <x:v>209000</x:v>
       </x:c>
-      <x:c r="J99" s="24" t="n">
+      <x:c r="J99" s="15" t="n">
         <x:f>ROUND(G99*12,2)</x:f>
         <x:v>394800</x:v>
       </x:c>
@@ -6671,7 +8222,7 @@
       <x:c r="M99" s="15" t="n">
         <x:v>7599</x:v>
       </x:c>
-      <x:c r="N99" s="15" t="n">
+      <x:c r="N99" s="80" t="n">
         <x:f>'Pass测算'!J38</x:f>
         <x:v>2200</x:v>
       </x:c>
@@ -6710,7 +8261,7 @@
       <x:c r="F100" s="12" t="n">
         <x:v>13.99</x:v>
       </x:c>
-      <x:c r="G100" s="23" t="n">
+      <x:c r="G100" s="12" t="n">
         <x:v>10.99</x:v>
       </x:c>
       <x:c r="H100" s="12" t="n">
@@ -6719,7 +8270,7 @@
       <x:c r="I100" s="12" t="n">
         <x:v>67.99</x:v>
       </x:c>
-      <x:c r="J100" s="23" t="n">
+      <x:c r="J100" s="12" t="n">
         <x:f>ROUND(G100*12,2)</x:f>
         <x:v>131.88</x:v>
       </x:c>
@@ -6732,7 +8283,7 @@
       <x:c r="M100" s="12" t="n">
         <x:v>2.49</x:v>
       </x:c>
-      <x:c r="N100" s="14" t="n">
+      <x:c r="N100" s="82" t="n">
         <x:f>'Pass测算'!J57</x:f>
         <x:v>0.53</x:v>
       </x:c>
@@ -6771,7 +8322,7 @@
       <x:c r="F101" s="15" t="n">
         <x:v>16900</x:v>
       </x:c>
-      <x:c r="G101" s="24" t="n">
+      <x:c r="G101" s="15" t="n">
         <x:v>12900</x:v>
       </x:c>
       <x:c r="H101" s="15" t="n">
@@ -6780,7 +8331,7 @@
       <x:c r="I101" s="15" t="n">
         <x:v>80900</x:v>
       </x:c>
-      <x:c r="J101" s="24" t="n">
+      <x:c r="J101" s="15" t="n">
         <x:f>ROUND(G101*12,2)</x:f>
         <x:v>154800</x:v>
       </x:c>
@@ -6793,7 +8344,7 @@
       <x:c r="M101" s="15" t="n">
         <x:v>2899</x:v>
       </x:c>
-      <x:c r="N101" s="15" t="n">
+      <x:c r="N101" s="80" t="n">
         <x:f>'Pass测算'!J19</x:f>
         <x:v>1300</x:v>
       </x:c>
@@ -6832,7 +8383,7 @@
       <x:c r="F102" s="15" t="n">
         <x:v>1199</x:v>
       </x:c>
-      <x:c r="G102" s="24" t="n">
+      <x:c r="G102" s="15" t="n">
         <x:v>909</x:v>
       </x:c>
       <x:c r="H102" s="15" t="n">
@@ -6841,7 +8392,7 @@
       <x:c r="I102" s="15" t="n">
         <x:v>5799</x:v>
       </x:c>
-      <x:c r="J102" s="24" t="n">
+      <x:c r="J102" s="15" t="n">
         <x:f>ROUND(G102*12,2)</x:f>
         <x:v>10908</x:v>
       </x:c>
@@ -6854,7 +8405,7 @@
       <x:c r="M102" s="15" t="n">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="N102" s="15" t="n">
+      <x:c r="N102" s="80" t="n">
         <x:f>'Pass测算'!J20</x:f>
         <x:v>92</x:v>
       </x:c>
@@ -6884,35 +8435,35 @@
       <x:c r="C103" s="13" t="str">
         <x:v>NOK</x:v>
       </x:c>
-      <x:c r="D103" s="15" t="n">
+      <x:c r="D103" s="83" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E103" s="15" t="n">
+      <x:c r="E103" s="83" t="n">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="F103" s="15" t="n">
+      <x:c r="F103" s="83" t="n">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="G103" s="24" t="n">
+      <x:c r="G103" s="83" t="n">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="H103" s="15" t="n">
+      <x:c r="H103" s="83" t="n">
         <x:v>905</x:v>
       </x:c>
-      <x:c r="I103" s="15" t="n">
+      <x:c r="I103" s="83" t="n">
         <x:v>1811</x:v>
       </x:c>
-      <x:c r="J103" s="24" t="n">
+      <x:c r="J103" s="83" t="n">
         <x:f>ROUND(G103*12,2)</x:f>
         <x:v>3396</x:v>
       </x:c>
-      <x:c r="K103" s="15" t="n">
+      <x:c r="K103" s="83" t="n">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="L103" s="15" t="n">
+      <x:c r="L103" s="83" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="M103" s="15" t="n">
+      <x:c r="M103" s="83" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="N103" s="14" t="n">
@@ -6942,41 +8493,41 @@
       <x:c r="B104" s="10" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="C104" s="13" t="str">
+      <x:c r="C104" s="86" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="D104" s="12" t="n">
+      <x:c r="D104" s="87" t="n">
         <x:v>1.49</x:v>
       </x:c>
-      <x:c r="E104" s="12" t="n">
+      <x:c r="E104" s="87" t="n">
         <x:v>9.99</x:v>
       </x:c>
-      <x:c r="F104" s="12" t="n">
+      <x:c r="F104" s="87" t="n">
         <x:v>19.99</x:v>
       </x:c>
-      <x:c r="G104" s="23" t="n">
+      <x:c r="G104" s="87" t="n">
         <x:v>14.99</x:v>
       </x:c>
-      <x:c r="H104" s="12" t="n">
+      <x:c r="H104" s="87" t="n">
         <x:v>47.99</x:v>
       </x:c>
-      <x:c r="I104" s="12" t="n">
+      <x:c r="I104" s="87" t="n">
         <x:v>95.99</x:v>
       </x:c>
-      <x:c r="J104" s="23" t="n">
+      <x:c r="J104" s="87" t="n">
         <x:f>ROUND(G104*12,2)</x:f>
         <x:v>179.88</x:v>
       </x:c>
-      <x:c r="K104" s="12" t="n">
+      <x:c r="K104" s="87" t="n">
         <x:v>4.99</x:v>
       </x:c>
-      <x:c r="L104" s="12" t="n">
+      <x:c r="L104" s="87" t="n">
         <x:v>2.49</x:v>
       </x:c>
-      <x:c r="M104" s="12" t="n">
+      <x:c r="M104" s="87" t="n">
         <x:v>3.49</x:v>
       </x:c>
-      <x:c r="N104" s="14" t="n">
+      <x:c r="N104" s="82" t="n">
         <x:f>'Pass测算'!J66</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -7011,7 +8562,7 @@
       <x:c r="F105" s="12" t="n">
         <x:v>71.99</x:v>
       </x:c>
-      <x:c r="G105" s="23" t="n">
+      <x:c r="G105" s="12" t="n">
         <x:v>53.99</x:v>
       </x:c>
       <x:c r="H105" s="12" t="n">
@@ -7020,7 +8571,7 @@
       <x:c r="I105" s="12" t="n">
         <x:v>346.99</x:v>
       </x:c>
-      <x:c r="J105" s="23" t="n">
+      <x:c r="J105" s="12" t="n">
         <x:f>ROUND(G105*12,2)</x:f>
         <x:v>647.88</x:v>
       </x:c>
@@ -7033,7 +8584,7 @@
       <x:c r="M105" s="12" t="n">
         <x:v>12.99</x:v>
       </x:c>
-      <x:c r="N105" s="14" t="n">
+      <x:c r="N105" s="82" t="n">
         <x:f>'Pass测算'!J58</x:f>
         <x:v>2.8</x:v>
       </x:c>
@@ -7072,7 +8623,7 @@
       <x:c r="F106" s="12" t="n">
         <x:v>77.99</x:v>
       </x:c>
-      <x:c r="G106" s="23" t="n">
+      <x:c r="G106" s="12" t="n">
         <x:v>57.99</x:v>
       </x:c>
       <x:c r="H106" s="12" t="n">
@@ -7081,7 +8632,7 @@
       <x:c r="I106" s="12" t="n">
         <x:v>372.99</x:v>
       </x:c>
-      <x:c r="J106" s="23" t="n">
+      <x:c r="J106" s="12" t="n">
         <x:f>ROUND(G106*12,2)</x:f>
         <x:v>695.88</x:v>
       </x:c>
@@ -7094,7 +8645,7 @@
       <x:c r="M106" s="12" t="n">
         <x:v>13.99</x:v>
       </x:c>
-      <x:c r="N106" s="14" t="n">
+      <x:c r="N106" s="82" t="n">
         <x:f>'Pass测算'!J70</x:f>
         <x:v>2.4</x:v>
       </x:c>
@@ -7133,7 +8684,7 @@
       <x:c r="F107" s="12" t="n">
         <x:v>21.99</x:v>
       </x:c>
-      <x:c r="G107" s="23" t="n">
+      <x:c r="G107" s="12" t="n">
         <x:v>16.99</x:v>
       </x:c>
       <x:c r="H107" s="12" t="n">
@@ -7142,7 +8693,7 @@
       <x:c r="I107" s="12" t="n">
         <x:v>105.99</x:v>
       </x:c>
-      <x:c r="J107" s="23" t="n">
+      <x:c r="J107" s="12" t="n">
         <x:f>ROUND(G107*12,2)</x:f>
         <x:v>203.88</x:v>
       </x:c>
@@ -7155,7 +8706,7 @@
       <x:c r="M107" s="12" t="n">
         <x:v>3.99</x:v>
       </x:c>
-      <x:c r="N107" s="14" t="n">
+      <x:c r="N107" s="82" t="n">
         <x:f>'Pass测算'!J77</x:f>
         <x:v>0.6</x:v>
       </x:c>
@@ -7194,7 +8745,7 @@
       <x:c r="F108" s="15" t="n">
         <x:v>1699</x:v>
       </x:c>
-      <x:c r="G108" s="24" t="n">
+      <x:c r="G108" s="15" t="n">
         <x:v>1299</x:v>
       </x:c>
       <x:c r="H108" s="15" t="n">
@@ -7203,7 +8754,7 @@
       <x:c r="I108" s="15" t="n">
         <x:v>7999</x:v>
       </x:c>
-      <x:c r="J108" s="24" t="n">
+      <x:c r="J108" s="15" t="n">
         <x:f>ROUND(G108*12,2)</x:f>
         <x:v>15588</x:v>
       </x:c>
@@ -7216,7 +8767,7 @@
       <x:c r="M108" s="15" t="n">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="N108" s="15" t="n">
+      <x:c r="N108" s="80" t="n">
         <x:f>'Pass测算'!J59</x:f>
         <x:v>63</x:v>
       </x:c>
@@ -7255,7 +8806,7 @@
       <x:c r="F109" s="12" t="n">
         <x:v>290.99</x:v>
       </x:c>
-      <x:c r="G109" s="23" t="n">
+      <x:c r="G109" s="12" t="n">
         <x:v>217.99</x:v>
       </x:c>
       <x:c r="H109" s="12" t="n">
@@ -7264,7 +8815,7 @@
       <x:c r="I109" s="12" t="n">
         <x:v>1397.99</x:v>
       </x:c>
-      <x:c r="J109" s="23" t="n">
+      <x:c r="J109" s="12" t="n">
         <x:f>ROUND(G109*12,2)</x:f>
         <x:v>2615.88</x:v>
       </x:c>
@@ -7277,7 +8828,7 @@
       <x:c r="M109" s="12" t="n">
         <x:v>50.99</x:v>
       </x:c>
-      <x:c r="N109" s="14" t="n">
+      <x:c r="N109" s="82" t="n">
         <x:f>'Pass测算'!J71</x:f>
         <x:v>8.8</x:v>
       </x:c>
@@ -7316,7 +8867,7 @@
       <x:c r="F110" s="12" t="n">
         <x:v>19.99</x:v>
       </x:c>
-      <x:c r="G110" s="23" t="n">
+      <x:c r="G110" s="12" t="n">
         <x:v>14.99</x:v>
       </x:c>
       <x:c r="H110" s="12" t="n">
@@ -7325,7 +8876,7 @@
       <x:c r="I110" s="12" t="n">
         <x:v>93.99</x:v>
       </x:c>
-      <x:c r="J110" s="23" t="n">
+      <x:c r="J110" s="12" t="n">
         <x:f>ROUND(G110*12,2)</x:f>
         <x:v>179.88</x:v>
       </x:c>
@@ -7338,7 +8889,7 @@
       <x:c r="M110" s="12" t="n">
         <x:v>3.49</x:v>
       </x:c>
-      <x:c r="N110" s="14" t="n">
+      <x:c r="N110" s="82" t="n">
         <x:f>'Pass测算'!J74</x:f>
         <x:v>0.53</x:v>
       </x:c>
@@ -7368,35 +8919,35 @@
       <x:c r="C111" s="18" t="str">
         <x:v>SEK</x:v>
       </x:c>
-      <x:c r="D111" s="19" t="n">
+      <x:c r="D111" s="84" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E111" s="19" t="n">
+      <x:c r="E111" s="84" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F111" s="19" t="n">
+      <x:c r="F111" s="84" t="n">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="G111" s="25" t="n">
+      <x:c r="G111" s="84" t="n">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="H111" s="19" t="n">
+      <x:c r="H111" s="84" t="n">
         <x:v>808</x:v>
       </x:c>
-      <x:c r="I111" s="19" t="n">
+      <x:c r="I111" s="84" t="n">
         <x:v>1616</x:v>
       </x:c>
-      <x:c r="J111" s="25" t="n">
+      <x:c r="J111" s="84" t="n">
         <x:f>ROUND(G111*12,2)</x:f>
         <x:v>3036</x:v>
       </x:c>
-      <x:c r="K111" s="19" t="n">
+      <x:c r="K111" s="84" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="L111" s="19" t="n">
+      <x:c r="L111" s="84" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="M111" s="19" t="n">
+      <x:c r="M111" s="84" t="n">
         <x:v>59</x:v>
       </x:c>
       <x:c r="N111" s="20" t="n">
@@ -7438,7 +8989,7 @@
       <x:c r="F112" s="12" t="n">
         <x:v>134.99</x:v>
       </x:c>
-      <x:c r="G112" s="23" t="n">
+      <x:c r="G112" s="12" t="n">
         <x:v>100.99</x:v>
       </x:c>
       <x:c r="H112" s="12" t="n">
@@ -7447,7 +8998,7 @@
       <x:c r="I112" s="12" t="n">
         <x:v>647.99</x:v>
       </x:c>
-      <x:c r="J112" s="23" t="n">
+      <x:c r="J112" s="12" t="n">
         <x:f>ROUND(G112*12,2)</x:f>
         <x:v>1211.88</x:v>
       </x:c>
@@ -7460,7 +9011,7 @@
       <x:c r="M112" s="12" t="n">
         <x:v>23.99</x:v>
       </x:c>
-      <x:c r="N112" s="14" t="n">
+      <x:c r="N112" s="82" t="n">
         <x:f>'Pass测算'!J72</x:f>
         <x:v>4.1</x:v>
       </x:c>
@@ -7499,7 +9050,7 @@
       <x:c r="F113" s="15" t="n">
         <x:v>95900</x:v>
       </x:c>
-      <x:c r="G113" s="24" t="n">
+      <x:c r="G113" s="15" t="n">
         <x:v>71900</x:v>
       </x:c>
       <x:c r="H113" s="15" t="n">
@@ -7508,7 +9059,7 @@
       <x:c r="I113" s="15" t="n">
         <x:v>459000</x:v>
       </x:c>
-      <x:c r="J113" s="24" t="n">
+      <x:c r="J113" s="15" t="n">
         <x:f>ROUND(G113*12,2)</x:f>
         <x:v>862800</x:v>
       </x:c>
@@ -7521,7 +9072,7 @@
       <x:c r="M113" s="15" t="n">
         <x:v>16900</x:v>
       </x:c>
-      <x:c r="N113" s="15" t="n">
+      <x:c r="N113" s="80" t="n">
         <x:f>'Pass测算'!J21</x:f>
         <x:v>7200</x:v>
       </x:c>
@@ -7560,7 +9111,7 @@
       <x:c r="F114" s="19" t="n">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="G114" s="25" t="n">
+      <x:c r="G114" s="19" t="n">
         <x:v>299</x:v>
       </x:c>
       <x:c r="H114" s="19" t="n">
@@ -7569,7 +9120,7 @@
       <x:c r="I114" s="19" t="n">
         <x:v>1929</x:v>
       </x:c>
-      <x:c r="J114" s="25" t="n">
+      <x:c r="J114" s="19" t="n">
         <x:f>ROUND(G114*12,2)</x:f>
         <x:v>3588</x:v>
       </x:c>
@@ -7582,7 +9133,7 @@
       <x:c r="M114" s="19" t="n">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="N114" s="19" t="n">
+      <x:c r="N114" s="85" t="n">
         <x:f>'Pass测算'!J36</x:f>
         <x:v>21</x:v>
       </x:c>
@@ -7621,7 +9172,7 @@
       <x:c r="F115" s="21" t="n">
         <x:v>27.99</x:v>
       </x:c>
-      <x:c r="G115" s="26" t="n">
+      <x:c r="G115" s="21" t="n">
         <x:v>20.99</x:v>
       </x:c>
       <x:c r="H115" s="21" t="n">
@@ -7630,7 +9181,7 @@
       <x:c r="I115" s="21" t="n">
         <x:v>136.99</x:v>
       </x:c>
-      <x:c r="J115" s="26" t="n">
+      <x:c r="J115" s="21" t="n">
         <x:f>ROUND(G115*12,2)</x:f>
         <x:v>251.88</x:v>
       </x:c>
@@ -7665,8 +9216,9 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d1390a4b6984a7c"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f54ca3a75734cd1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R494c1910003c4a46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40779,7 +42331,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ea9dce01d804199"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05449fb6087f41f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42195,7 +43747,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb29e679637840cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fed001587f64044"/>
   </x:tableParts>
 </x:worksheet>
 </file>